--- a/workspaces/btc_daily_14days/drawdown/drawdown_60.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_60.xlsx
@@ -575,46 +575,46 @@
         <v>30</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24.1732283464567</v>
+        <v>24.09476040891471</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.7718388635030067</v>
+        <v>-0.7697554358955827</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.502939103527034</v>
+        <v>5.484610772100076</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.3064614308721</v>
+        <v>12.26563158827116</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.575914025452882</v>
+        <v>-1.572018456662647</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.29090649714647</v>
+        <v>-11.2554605776472</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.701941605712541</v>
+        <v>-4.687639213888993</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-18.52758129313212</v>
+        <v>-18.46866518314121</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.91358072063483</v>
+        <v>-11.87557153641227</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.10892587852754</v>
+        <v>-16.05797034656256</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-23.00130950910205</v>
+        <v>-22.92819679886851</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-22.9724678876177</v>
+        <v>-22.89945269956942</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-26.74312263558946</v>
+        <v>-26.65770300920954</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-26.49907380184868</v>
+        <v>-26.41455241742309</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.874390701163442</v>
+        <v>-4.859328501385946</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.487564674544494</v>
+        <v>-6.466759989122842</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.408710453651558</v>
+        <v>7.38382072735196</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.775633028092173</v>
+        <v>2.76521832770112</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1459260391463246</v>
+        <v>-0.1466342829956417</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.616094877304405</v>
+        <v>-4.601825836068627</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.702061293316177</v>
+        <v>-4.687499578345196</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-19.48221685481695</v>
+        <v>-19.41911361326376</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.77690680834021</v>
+        <v>-14.72884987445796</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-15.63229543837365</v>
+        <v>-15.58197540991312</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.84146742747656</v>
+        <v>-15.79043513764169</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-15.81092110314439</v>
+        <v>-15.75999367336906</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-21.01297454834402</v>
+        <v>-20.94473915933786</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-25.54510470297382</v>
+        <v>-25.46217146504365</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.052016225245943</v>
+        <v>2.044534402439432</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.502711560239369</v>
+        <v>6.481094024653153</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.049779269965839</v>
+        <v>-9.020892719153466</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.921530393443987</v>
+        <v>-8.893587583197466</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-12.49610977408418</v>
+        <v>-12.45612347679082</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-9.167423725799196</v>
+        <v>-9.137881496652177</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-12.28948941372147</v>
+        <v>-12.24964151868375</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.725286193032446</v>
+        <v>-9.693143234311179</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.716072376091063</v>
+        <v>-3.703559706300915</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.56875044041999</v>
+        <v>-4.553940574949223</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.737188495445636</v>
+        <v>-1.731675527207102</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.74190752454632</v>
+        <v>-4.72649673252451</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.165087790931778</v>
+        <v>-5.147791771517163</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.956238776948616</v>
+        <v>-7.929703932576118</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.044408143094209</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.621572546024588</v>
+        <v>-5.603254275923149</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.04570605747148448</v>
+        <v>0.04484707085104134</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.889010034942892</v>
+        <v>-5.870675646886596</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.429506683831306</v>
+        <v>-6.409010732883544</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.06506951780883696</v>
+        <v>-0.06528459307919121</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1499639904496846</v>
+        <v>-0.149794916539399</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.453103521690053</v>
+        <v>5.435336577313734</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.393340190563443</v>
+        <v>5.375784712269692</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.505661042435307</v>
+        <v>1.500529742434345</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.376952895322368</v>
+        <v>7.352263873743347</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.413271955604728</v>
+        <v>7.388539505244417</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.125728615554358</v>
+        <v>-2.118243419970788</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.204948833706112</v>
+        <v>4.191508188637386</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>37</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.844789671561941</v>
+        <v>-3.832747286261935</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.161156091739656</v>
+        <v>-8.133984733099275</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.150044594213838</v>
+        <v>-3.140195106543096</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.83955127677515</v>
+        <v>-13.79420593277908</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-8.971147481497496</v>
+        <v>-8.941752189574117</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-11.38188543775355</v>
+        <v>-11.34412850690975</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-8.762813467410695</v>
+        <v>-8.733739159020466</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-11.94097064081839</v>
+        <v>-11.90068924291207</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-17.4218017566975</v>
+        <v>-17.36311356905532</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-23.69614825499006</v>
+        <v>-23.61680244351228</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-21.1976924993206</v>
+        <v>-21.12693955945912</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-26.58953281587707</v>
+        <v>-26.50060878959929</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-24.30758550955855</v>
+        <v>-24.22552930124531</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-21.35149364990249</v>
+        <v>-21.27941728229069</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.792275965504963</v>
+        <v>1.785455417348615</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.392915892903034</v>
+        <v>-8.364450130711717</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.931444816822328</v>
+        <v>-5.911991951707662</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.943201655081474</v>
+        <v>-2.933904156960843</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.482973294006428</v>
+        <v>-3.471611292892106</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-11.76876205715641</v>
+        <v>-11.72898691972962</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-14.7183189847921</v>
+        <v>-14.66853227162654</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.465821797520526</v>
+        <v>-9.43316651951725</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.529584826516519</v>
+        <v>-9.496521351191731</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-18.97568732031849</v>
+        <v>-18.91083827719773</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-13.45654101840583</v>
+        <v>-13.41067496512464</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-16.29116551120681</v>
+        <v>-16.23544707103671</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.71771398877087</v>
+        <v>-16.65982039644398</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-16.47145530234658</v>
+        <v>-16.4145524174246</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>30</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-9.16010498687664</v>
+        <v>-9.12966178686986</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.896512517147762</v>
+        <v>5.876694662961832</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.167994998283469</v>
+        <v>2.160136684255612</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.37293576803701</v>
+        <v>-4.358599970926292</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.760568761678108</v>
+        <v>1.754228605624064</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.058651668405702</v>
+        <v>2.051913024132958</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.364342370206657</v>
+        <v>-1.359282766423377</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.833047087835013</v>
+        <v>-1.825884978158861</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.235198303161553</v>
+        <v>-5.216227214002764</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.430089354722817</v>
+        <v>-9.396712505289919</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.295485594745557</v>
+        <v>-6.273277306508177</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.26300977508717</v>
+        <v>-6.240566295786955</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.344578975267275</v>
+        <v>3.334988523218428</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.940812342317869</v>
+        <v>6.91878091590722</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>47</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.95337019042833</v>
+        <v>4.935665848992073</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.9137772032997731</v>
+        <v>-0.9104669895464141</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.309006047053636</v>
+        <v>-1.305010048641108</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7.338463412395775</v>
+        <v>7.312622619134046</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4116567102680904</v>
+        <v>0.4098480971851046</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-9.943062127264135</v>
+        <v>-9.908465470172658</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-10.03069436924766</v>
+        <v>-9.99558368479498</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-12.63336415018075</v>
+        <v>-12.58873377781116</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-12.69811587236299</v>
+        <v>-12.65296756303763</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.288379315169642</v>
+        <v>-9.254809008294302</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-11.62916195718461</v>
+        <v>-11.58806801479716</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.196450089514407</v>
+        <v>-5.177232853704609</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.351069036012845</v>
+        <v>-1.344629461657242</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.100709472110907</v>
+        <v>-1.095403481254387</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>45</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-12.49343832020998</v>
+        <v>-12.45056162553466</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.673739108979056</v>
+        <v>3.66108667210294</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.056317636336935</v>
+        <v>1.0521399527398</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.708994824203259</v>
+        <v>-7.682847561478852</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.576284414988905</v>
+        <v>-1.571185080206462</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9459606115138115</v>
+        <v>0.9433298262716932</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.087005911556616</v>
+        <v>3.077107201153396</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3929367430969961</v>
+        <v>0.3931130080279175</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.785634773401412</v>
+        <v>4.770752113143736</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5206803434505645</v>
+        <v>-0.5169436707966071</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.958744276710156</v>
+        <v>5.939342620943698</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.223476702971226</v>
+        <v>8.196234142545123</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.803634482417245</v>
+        <v>7.778215379103493</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.826459872678946</v>
+        <v>5.807669804798628</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>50</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.506561679790032</v>
+        <v>3.493827053494336</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.106135045684645</v>
+        <v>-4.091534583050638</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.501161535221968</v>
+        <v>-2.492835714786111</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.373088682040297</v>
+        <v>-4.358090257572648</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.915482446879253</v>
+        <v>-6.891322841787826</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.614423358278572</v>
+        <v>-2.604500266505937</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-10.71323366526214</v>
+        <v>-10.6744651444101</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-11.18472206533279</v>
+        <v>-11.14349690220906</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.231618557230057</v>
+        <v>-3.218464555209401</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.085051032434492</v>
+        <v>-4.068581389270619</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.2801048005613112</v>
+        <v>-0.2778915447643584</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.251793509018256</v>
+        <v>-2.242605616889797</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.674491021808066</v>
+        <v>-2.663422310357866</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.596820071789807</v>
+        <v>3.585447582574488</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>64</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.618438320209975</v>
+        <v>-5.598651921638123</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5826307691891159</v>
+        <v>0.5807756384694969</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.31452618427717</v>
+        <v>3.302131827964686</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.318207964088522</v>
+        <v>0.3167542553308849</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.036161080598035</v>
+        <v>6.014354221388629</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.90004715606041</v>
+        <v>7.872346910550789</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7.817058294528557</v>
+        <v>7.79019423583437</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.350586446685405</v>
+        <v>7.326238658919017</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.593559383288458</v>
+        <v>2.58611173196649</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.308055579997117</v>
+        <v>3.298371227423203</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.53738571279662</v>
+        <v>1.533111301229525</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.841274759854386</v>
+        <v>7.814336516042772</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.718146190938974</v>
+        <v>2.710107921911863</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.734556261420195</v>
+        <v>-1.727052417423891</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.506561679789719</v>
+        <v>3.542233369083469</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5617971529791461</v>
+        <v>0.5668549693439076</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.503342136784831</v>
+        <v>5.560568196169427</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9.63864672451539</v>
+        <v>9.736595737357796</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>7.767555139223326</v>
+        <v>7.846902936226428</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>8.067370714886415</v>
+        <v>8.147708197150564</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>10.65570776434225</v>
+        <v>10.76056101525042</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>11.52605430759693</v>
+        <v>11.63721942549547</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>16.81348468460573</v>
+        <v>16.97777229058324</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>18.63909619741685</v>
+        <v>18.82091947768674</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>19.77671403378488</v>
+        <v>19.97245148640695</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>15.80450147350369</v>
+        <v>15.96115032979255</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>14.04864430577209</v>
+        <v>14.18552341588592</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15.059325533273</v>
+        <v>15.20706920419703</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>100</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.493438320209755</v>
+        <v>-1.488604181186815</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8952350257763513</v>
+        <v>0.8922715183670817</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.501171671489949</v>
+        <v>1.494857803927857</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.634689933433101</v>
+        <v>4.617420171047634</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>9.102902883310151</v>
+        <v>9.070048066672541</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.400308506996481</v>
+        <v>7.374111807356968</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7.317435831723039</v>
+        <v>7.291883164692969</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5.848913467617017</v>
+        <v>5.829306550718726</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>13.80836084907614</v>
+        <v>13.76053389532817</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>10.9546066989116</v>
+        <v>10.91693247131768</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>8.747353401171452</v>
+        <v>8.716446564443643</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>8.784452046271014</v>
+        <v>8.753392571696082</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.357414990697187</v>
+        <v>6.335726250298876</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>12.62941254169186</v>
+        <v>12.58544758257563</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8540940579148923</v>
+        <v>-0.893044337529858</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.841659672677892</v>
+        <v>-2.984411804975089</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.612261373408586</v>
+        <v>-3.774517845119114</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.892782347186092</v>
+        <v>4.108752084581333</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.986915741680072</v>
+        <v>3.16342802931522</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.008295622408532</v>
+        <v>7.372436944165621</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.651258238689984</v>
+        <v>3.842863469613249</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.209065699693106</v>
+        <v>3.364718137077553</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.140278584234267</v>
+        <v>3.309304276774917</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.96374392259694</v>
+        <v>4.167257701210474</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>6.223316054805046</v>
+        <v>6.550233122877124</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.715396110761347</v>
+        <v>7.067213743485965</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>10.07430022671273</v>
+        <v>10.57710556064414</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7.014368030576911</v>
+        <v>7.378551030851064</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.4051124044277046</v>
+        <v>0.4146440664716593</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2428141537822839</v>
+        <v>0.2452180333595706</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.746496171823381</v>
+        <v>2.809863555560248</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.980011422618702</v>
+        <v>-4.05179546341077</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.616593088478993</v>
+        <v>-1.636347213960732</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.8534463628851157</v>
+        <v>0.8837276337934767</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4402878099599974</v>
+        <v>0.4568081708365739</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.434050068825464</v>
+        <v>1.465184838787359</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.255933305910887</v>
+        <v>-2.295847810298682</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5329291695898135</v>
+        <v>0.5500453071668261</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.632043601157029</v>
+        <v>3.721597703898745</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.665165433111568</v>
+        <v>3.755980861244012</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.434128363331268</v>
+        <v>5.557948472521332</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.949695876351498</v>
+        <v>5.066929064056879</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.048993875765532</v>
+        <v>-8.243777073597386</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-7.27961510777741</v>
+        <v>-7.460210257884796</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.325277465167822</v>
+        <v>-1.348704241643368</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.979578842043026</v>
+        <v>2.038970669727533</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.305088750048256</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.268589046160685</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7270865335381416</v>
+        <v>-0.7357753379585787</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.211030762845105</v>
+        <v>3.291656789007007</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.203894516846795</v>
+        <v>1.240481472374313</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.603323871065598</v>
+        <v>1.649928263988329</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.186203135328476</v>
+        <v>2.258183069752235</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1618706395460592</v>
+        <v>-0.1464581631464128</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.5685842890825228</v>
+        <v>-0.5667127740911297</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.503245714648443</v>
+        <v>-3.569023962139859</v>
       </c>
     </row>
     <row r="22">
@@ -2185,10 +2185,8 @@
           <t>X &gt; -0.4278</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4036~4049</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4036</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.08543634441348047</v>
@@ -2239,10 +2237,8 @@
           <t>X &gt; -0.413</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4006~4019</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4006</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2665162002796464</v>
@@ -2293,10 +2289,8 @@
           <t>X &gt; -0.3983</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3964~3977</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3964</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2178537086937524</v>
@@ -2347,10 +2341,8 @@
           <t>X &gt; -0.3835</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3931~3944</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3931</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2368460281207234</v>
@@ -2401,10 +2393,8 @@
           <t>X &gt; -0.3688</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3898~3911</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3898</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.2561588520432636</v>
@@ -2455,10 +2445,8 @@
           <t>X &gt; -0.354</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3861~3874</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3861</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2218843708036715</v>
@@ -2509,10 +2497,8 @@
           <t>X &gt; -0.3393</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3826~3839</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3826</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.2402473850706173</v>
@@ -2563,10 +2549,8 @@
           <t>X &gt; -0.3245</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3796~3809</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3796</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1699938465948563</v>
@@ -2617,10 +2601,8 @@
           <t>X &gt; -0.3098</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3749~3762</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3749</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.2340018502471892</v>
@@ -2671,10 +2653,8 @@
           <t>X &gt; -0.295</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3704~3717</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3704</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.08558252252366572</v>
@@ -2725,10 +2705,8 @@
           <t>X &gt; -0.2803</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3654~3667</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3654</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.1345618544341391</v>
@@ -2779,10 +2757,8 @@
           <t>X &gt; -0.2655</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3590~3603</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3590</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.03715189223328963</v>
@@ -2833,10 +2809,8 @@
           <t>X &gt; -0.2508</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3516~3528</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3516</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -2887,10 +2861,8 @@
           <t>X &gt; -0.236</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3416~3428</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3416</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.07220144739783763</v>
@@ -2941,10 +2913,8 @@
           <t>X &gt; -0.2213</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3300~3306</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3300</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.04334757610834572</v>
@@ -2995,10 +2965,8 @@
           <t>X &gt; -0.2065</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3165~3168</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3165</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.06288276465441811</v>
@@ -3049,10 +3017,8 @@
           <t>X &gt; -0.1918</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3042~3042</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3042</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.2679029026697108</v>
@@ -3103,10 +3069,8 @@
           <t>X &gt; -0.177</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2907~2907</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2907</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.619736774389267</v>
@@ -3157,10 +3121,8 @@
           <t>X &gt; -0.1623</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2770~2770</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2770</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.7917602357467075</v>
@@ -3211,10 +3173,8 @@
           <t>X &gt; -0.1475</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2623~2623</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2623</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.6518152062864075</v>
@@ -3265,10 +3225,8 @@
           <t>X &gt; -0.1328</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2449~2449</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2449</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.9161166001656937</v>
@@ -3319,10 +3277,8 @@
           <t>X &gt; -0.118</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2273~2273</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2273</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.048136690788702</v>
@@ -3373,10 +3329,8 @@
           <t>X &gt; -0.1033</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2077~2077</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2077</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.286051328321555</v>
@@ -3427,10 +3381,8 @@
           <t>X &gt; -0.0885</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1889~1889</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1889</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.821013770843493</v>
@@ -3481,10 +3433,8 @@
           <t>X &gt; -0.07375</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1684~1684</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1684</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.910362154849409</v>
@@ -3535,10 +3485,8 @@
           <t>X &gt; -0.059</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1478~1478</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1478</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>3.528212559357009</v>
@@ -3589,10 +3537,8 @@
           <t>X &gt; -0.04425</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1228~1228</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1228</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.12545418793335</v>
@@ -3643,10 +3589,8 @@
           <t>X &gt; -0.0295</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1002~1002</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1002</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.095384035079448</v>
@@ -3697,10 +3641,8 @@
           <t>X &gt; -0.01475</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>716~716</t>
-        </is>
+      <c r="B34" t="n">
+        <v>716</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.696505813868242</v>
@@ -3751,10 +3693,8 @@
           <t>X &gt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0~0</t>
-        </is>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -3911,10 +3851,8 @@
           <t>X &lt; -0.4278</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>6.54270625810328</v>
@@ -3965,10 +3903,8 @@
           <t>X &lt; -0.413</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>113~113</t>
-        </is>
+      <c r="B7" t="n">
+        <v>113</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>11.22337583908206</v>
@@ -4019,10 +3955,8 @@
           <t>X &lt; -0.3983</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>155~155</t>
-        </is>
+      <c r="B8" t="n">
+        <v>155</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6.861400389467441</v>
@@ -4073,10 +4007,8 @@
           <t>X &lt; -0.3835</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>188~188</t>
-        </is>
+      <c r="B9" t="n">
+        <v>188</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.017199977662365</v>
@@ -4127,10 +4059,8 @@
           <t>X &lt; -0.3688</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>221~221</t>
-        </is>
+      <c r="B10" t="n">
+        <v>221</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>5.425113715989127</v>
@@ -4181,10 +4111,8 @@
           <t>X &lt; -0.354</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>258~258</t>
-        </is>
+      <c r="B11" t="n">
+        <v>258</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>4.095708966611731</v>
@@ -4235,10 +4163,8 @@
           <t>X &lt; -0.3393</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>293~293</t>
-        </is>
+      <c r="B12" t="n">
+        <v>293</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>3.820554853851462</v>
@@ -4289,10 +4215,8 @@
           <t>X &lt; -0.3245</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>323~323</t>
-        </is>
+      <c r="B13" t="n">
+        <v>323</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2.614920812916964</v>
@@ -4343,10 +4267,8 @@
           <t>X &lt; -0.3098</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>370~370</t>
-        </is>
+      <c r="B14" t="n">
+        <v>370</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.911967085195428</v>
@@ -4397,10 +4319,8 @@
           <t>X &lt; -0.295</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>415~415</t>
-        </is>
+      <c r="B15" t="n">
+        <v>415</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.241501438826177</v>
@@ -4451,10 +4371,8 @@
           <t>X &lt; -0.2803</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>465~465</t>
-        </is>
+      <c r="B16" t="n">
+        <v>465</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.485056303445937</v>
@@ -4505,10 +4423,8 @@
           <t>X &lt; -0.2655</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>529~529</t>
-        </is>
+      <c r="B17" t="n">
+        <v>529</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.6256543073892686</v>
@@ -4559,10 +4475,8 @@
           <t>X &lt; -0.2508</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>603~604</t>
-        </is>
+      <c r="B18" t="n">
+        <v>603</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.9833828718430055</v>
@@ -4613,10 +4527,8 @@
           <t>X &lt; -0.236</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>703~704</t>
-        </is>
+      <c r="B19" t="n">
+        <v>703</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.6315616797900248</v>
@@ -4667,10 +4579,8 @@
           <t>X &lt; -0.2213</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>819~826</t>
-        </is>
+      <c r="B20" t="n">
+        <v>819</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.4121306870539456</v>
@@ -4721,10 +4631,8 @@
           <t>X &lt; -0.2065</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>954~964</t>
-        </is>
+      <c r="B21" t="n">
+        <v>954</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.4111259951427257</v>
@@ -4775,10 +4683,8 @@
           <t>X &lt; -0.1918</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1077~1090</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1077</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.5668328156228242</v>
@@ -4829,10 +4735,8 @@
           <t>X &lt; -0.177</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1212~1225</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1212</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.309764850822219</v>
@@ -4883,10 +4787,8 @@
           <t>X &lt; -0.1623</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1349~1362</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1349</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.465538173367101</v>
@@ -4937,10 +4839,8 @@
           <t>X &lt; -0.1475</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1496~1509</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1496</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.002384642277569</v>
@@ -4991,10 +4891,8 @@
           <t>X &lt; -0.1328</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1670~1683</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1670</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.215957630964581</v>
@@ -5045,10 +4943,8 @@
           <t>X &lt; -0.118</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1846~1859</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1846</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.175525463835584</v>
@@ -5099,10 +4995,8 @@
           <t>X &lt; -0.1033</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2042~2055</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2042</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.203900607314601</v>
@@ -5153,10 +5047,8 @@
           <t>X &lt; -0.0885</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2230~2243</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2230</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.445734352309834</v>
@@ -5207,10 +5099,8 @@
           <t>X &lt; -0.07375</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2435~2448</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2435</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.921542895373378</v>
@@ -5261,10 +5151,8 @@
           <t>X &lt; -0.059</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2641~2654</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2641</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.890574718099948</v>
@@ -5315,10 +5203,8 @@
           <t>X &lt; -0.04425</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2891~2904</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2891</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.253768898722377</v>
@@ -5369,10 +5255,8 @@
           <t>X &lt; -0.0295</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3117~3130</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3117</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.9279431125422448</v>
@@ -5423,10 +5307,8 @@
           <t>X &lt; -0.01475</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3403~3416</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3403</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.2978879689219198</v>
@@ -5477,10 +5359,8 @@
           <t>X &lt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3705~3718</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3705</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.09967823414220334</v>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_60.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_60.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-60 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-60 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>30</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24.09476040891471</v>
+        <v>24.10726037140642</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.7697554358955827</v>
+        <v>-0.7568859088084778</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.484610772100076</v>
+        <v>5.497585015246415</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.26563158827116</v>
+        <v>12.27858529962281</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.572018456662647</v>
+        <v>-1.558938530995555</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.2554605776472</v>
+        <v>-11.2424498509914</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.687639213888993</v>
+        <v>-4.674598343620502</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-18.46866518314121</v>
+        <v>-18.45551123356132</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.87557153641227</v>
+        <v>-11.8623934179837</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.05797034656256</v>
+        <v>-16.04458287813332</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-22.92819679886851</v>
+        <v>-22.91475406060236</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-22.89945269956942</v>
+        <v>-22.88601011045873</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-26.65770300920954</v>
+        <v>-26.64415208273255</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-26.41455241742309</v>
+        <v>-26.42498205312124</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.859328501385946</v>
+        <v>-4.846852454855835</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.466759989122842</v>
+        <v>-6.453895536590018</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.38382072735196</v>
+        <v>7.396795771303843</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.76521832770112</v>
+        <v>2.778165692562595</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1466342829956417</v>
+        <v>-0.1335541147548369</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.601825836068627</v>
+        <v>-4.588812412274891</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.687499578345196</v>
+        <v>-4.674459203368905</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-19.41911361326376</v>
+        <v>-19.40596064097577</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.72884987445796</v>
+        <v>-14.71567310343064</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-15.58197540991312</v>
+        <v>-15.56858821256288</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.79043513764169</v>
+        <v>-15.77699137934453</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-15.75999367336906</v>
+        <v>-15.74655040370621</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-20.94473915933786</v>
+        <v>-20.93118799250979</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-25.46217146504365</v>
+        <v>-25.47260110074288</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.044534402439432</v>
+        <v>2.057015284404628</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.481094024653153</v>
+        <v>6.493967543415891</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.020892719153466</v>
+        <v>-9.007929825738678</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.893587583197466</v>
+        <v>-8.880648307908082</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-12.45612347679082</v>
+        <v>-12.44305104030563</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-9.137881496652177</v>
+        <v>-9.124871019390163</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-12.24964151868375</v>
+        <v>-12.23660509307825</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.693143234311179</v>
+        <v>-9.679987167409294</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.703559706300915</v>
+        <v>-3.690379881353692</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.553940574949223</v>
+        <v>-4.540550943291919</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.731675527207102</v>
+        <v>-1.718229357398428</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.72649673252451</v>
+        <v>-4.713052245863359</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.147791771517163</v>
+        <v>-5.134239701447456</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.929703932576118</v>
+        <v>-7.94013356827427</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.044408143094209</v>
+        <v>2.056888358736721</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.603254275923149</v>
+        <v>-5.59039079526859</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.04484707085104134</v>
+        <v>0.05781565469995087</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.870675646886596</v>
+        <v>-5.857735153929873</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.409010732883544</v>
+        <v>-6.395935491632443</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.06528459307919121</v>
+        <v>-0.05226997644358988</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.149794916539399</v>
+        <v>-0.1367535250308265</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.435336577313734</v>
+        <v>5.448498121585445</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.375784712269692</v>
+        <v>5.388967179719323</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.500529742434345</v>
+        <v>1.513920684112648</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.352263873743347</v>
+        <v>7.365711641583822</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.388539505244417</v>
+        <v>7.401985443056738</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.118243419970788</v>
+        <v>-2.104691223685272</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.191508188637386</v>
+        <v>4.181078552937855</v>
       </c>
     </row>
     <row r="10">
@@ -783,202 +783,202 @@
         <v>37</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.832747286261935</v>
+        <v>-3.820272901753647</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.133984733099275</v>
+        <v>-8.121124199035442</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.140195106543096</v>
+        <v>-3.12722955893409</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.79420593277908</v>
+        <v>-13.78127150467735</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-8.941752189574117</v>
+        <v>-8.928679183013628</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-11.34412850690975</v>
+        <v>-11.33112043987723</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-8.733739159020466</v>
+        <v>-8.720702240180316</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-11.90068924291207</v>
+        <v>-11.88753497735892</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-17.36311356905532</v>
+        <v>-17.34993897941438</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-23.61680244351228</v>
+        <v>-23.60341848217076</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-21.12693955945912</v>
+        <v>-21.11349766274081</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-26.50060878959929</v>
+        <v>-26.48716749210175</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-24.22552930124531</v>
+        <v>-24.21197865964094</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-21.27941728229069</v>
+        <v>-21.28984691798762</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.3467</t>
+          <t>X ≈ -0.3466</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.785455417348615</v>
+        <v>1.797933815856489</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.364450130711717</v>
+        <v>-8.35159083203915</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.911991951707662</v>
+        <v>-5.899029301428172</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.933904156960843</v>
+        <v>-2.920963341138147</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.471611292892106</v>
+        <v>-3.45853574119964</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-11.72898691972962</v>
+        <v>-11.71597983044955</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-14.66853227162654</v>
+        <v>-14.65549881261362</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.43316651951725</v>
+        <v>-9.420011838051167</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.496521351191731</v>
+        <v>-9.483344643359793</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-18.91083827719773</v>
+        <v>-18.89745354932786</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-13.41067496512464</v>
+        <v>-13.39723185834033</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-16.23544707103671</v>
+        <v>-16.2220046460426</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.65982039644398</v>
+        <v>-16.64626937095268</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-16.4145524174246</v>
+        <v>-16.42498205312405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.3319</t>
+          <t>X ≈ -0.3318</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>30</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-9.12966178686986</v>
+        <v>-9.117193917675252</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.876694662961832</v>
+        <v>5.889564800770081</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.160136684255612</v>
+        <v>2.173104643928923</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.358599970926292</v>
+        <v>-4.345660827507579</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.754228605624064</v>
+        <v>1.767306775269098</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.051913024132958</v>
+        <v>2.064927024427007</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.359282766423377</v>
+        <v>-1.346243536608959</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.825884978158861</v>
+        <v>-1.812727652786258</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.216227214002764</v>
+        <v>-5.203049457215073</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.396712505289919</v>
+        <v>-9.383325578589059</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.273277306508177</v>
+        <v>-6.259833005687689</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.240566295786955</v>
+        <v>-6.227122692039423</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.334988523218428</v>
+        <v>3.348540829574716</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.91878091590722</v>
+        <v>6.908351280213608</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.3172</t>
+          <t>X ≈ -0.3171</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.935665848992073</v>
+        <v>3.755467873431861</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.9104669895464141</v>
+        <v>-2.002222839013108</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.305010048641108</v>
+        <v>-2.396958752556756</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7.312622619134046</v>
+        <v>6.043522562021863</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4098480971851046</v>
+        <v>-0.7267977787309121</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-9.908465470172658</v>
+        <v>-8.745424952011703</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.99558368479498</v>
+        <v>-8.832209884996246</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-12.58873377781116</v>
+        <v>-11.38067989728086</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-12.65296756303763</v>
+        <v>-11.4445738322643</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.254809008294302</v>
+        <v>-8.134444783300196</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-11.58806801479716</v>
+        <v>-10.42306184300136</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.177232853704609</v>
+        <v>-6.227051072650745</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.344629461657242</v>
+        <v>-2.48325237071726</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.095403481254387</v>
+        <v>-2.25831538645798</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-12.45056162553466</v>
+        <v>-11.53213859850283</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.66108667210294</v>
+        <v>4.982891610633267</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.0521399527398</v>
+        <v>2.324036706868846</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.682847561478852</v>
+        <v>-6.612122701377245</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.571185080206462</v>
+        <v>-0.3488913031341454</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9433298262716932</v>
+        <v>-0.05160884472048366</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.077107201153396</v>
+        <v>2.132338307633923</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3931130080279175</v>
+        <v>-0.6022169260149326</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.770752113143736</v>
+        <v>3.876050775186989</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5169436707966071</v>
+        <v>-1.512579247800261</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.939342620943698</v>
+        <v>5.094888348820199</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.196234142545123</v>
+        <v>9.673543820711167</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.778215379103493</v>
+        <v>9.256023208193369</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.807669804798628</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>50</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.493827053494336</v>
+        <v>3.506302857447373</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.091534583050638</v>
+        <v>-4.07867609343117</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.492835714786111</v>
+        <v>-2.479874388638528</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.358090257572648</v>
+        <v>-4.345154090785627</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.891322841787826</v>
+        <v>-6.87825285038236</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.604500266505937</v>
+        <v>-2.591491268094103</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-10.6744651444101</v>
+        <v>-10.66143287100583</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-11.14349690220906</v>
+        <v>-11.13034564772557</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.218464555209401</v>
+        <v>-3.20528770963611</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.068581389270619</v>
+        <v>-4.05519433904189</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.2778915447643584</v>
+        <v>-0.2644469142353643</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.242605616889797</v>
+        <v>-2.229162062560249</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.663422310357866</v>
+        <v>-2.649870712072001</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.585447582574488</v>
+        <v>3.575017946879065</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>64</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.598651921638123</v>
+        <v>-5.586186611688326</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5807756384694969</v>
+        <v>0.5936367201793615</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.302131827964686</v>
+        <v>3.315096571841345</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3167542553308849</v>
+        <v>0.3296925760373668</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.014354221388629</v>
+        <v>6.027431760086778</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.872346910550789</v>
+        <v>7.885361268359091</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7.79019423583437</v>
+        <v>7.803235254874565</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.326238658919017</v>
+        <v>7.339397384181503</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.58611173196649</v>
+        <v>2.59929008695687</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.298371227423203</v>
+        <v>3.311759942900238</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.533111301229525</v>
+        <v>1.546555946656966</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.814336516042772</v>
+        <v>7.827781340103236</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.710107921911863</v>
+        <v>2.723659788208053</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.727052417423891</v>
+        <v>-1.737482053123465</v>
       </c>
     </row>
     <row r="17">
@@ -1144,101 +1144,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.542233369083469</v>
+        <v>3.505976150911863</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5668549693439076</v>
+        <v>0.5728048605666132</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.560568196169427</v>
+        <v>5.495359214638057</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9.736595737357796</v>
+        <v>9.615735937005788</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>7.846902936226428</v>
+        <v>7.751586904834475</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>8.147708197150564</v>
+        <v>8.050976080154271</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>10.76056101525042</v>
+        <v>10.63036719379866</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>11.63721942549547</v>
+        <v>11.49852143253072</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>16.97777229058324</v>
+        <v>16.76652922462603</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>18.82091947768674</v>
+        <v>18.58593139926236</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>19.97245148640695</v>
+        <v>19.71851136919675</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>15.96115032979255</v>
+        <v>15.76060479048119</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>14.18552341588592</v>
+        <v>14.01209125574354</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15.20706920419703</v>
+        <v>15.57501794687725</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.2434</t>
+          <t>X ≈ -0.2433</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>100</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.488604181186815</v>
+        <v>-1.997961825122864</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8922715183670817</v>
+        <v>0.9048815006566997</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.494857803927857</v>
+        <v>1.507291145343103</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.617420171047634</v>
+        <v>4.628919606827367</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>9.070048066672541</v>
+        <v>9.080387443220097</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.374111807356968</v>
+        <v>7.384940593724473</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7.291883164692969</v>
+        <v>7.302792625357213</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5.829306550718726</v>
+        <v>5.840828930095988</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>13.76053389532817</v>
+        <v>13.76972989626378</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>10.91693247131768</v>
+        <v>10.92718305645374</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>8.716446564443643</v>
+        <v>8.727316535921304</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>8.753392571696082</v>
+        <v>8.764248745159527</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.335726250298876</v>
+        <v>6.347470701995483</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>12.58544758257563</v>
+        <v>12.57501794687747</v>
       </c>
     </row>
     <row r="19">
@@ -1251,98 +1251,98 @@
         <v>116</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.893044337529858</v>
+        <v>-0.8805220478542353</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.984411804975089</v>
+        <v>-3.436497622854382</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.774517845119114</v>
+        <v>-4.226777792194646</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.108752084581333</v>
+        <v>4.120867750501269</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.16342802931522</v>
+        <v>2.709221474224009</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.372436944165621</v>
+        <v>6.918391950714287</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.842863469613249</v>
+        <v>3.854957976358513</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.364718137077553</v>
+        <v>3.377164811704105</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.309304276774917</v>
+        <v>3.321686780657359</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.167257701210474</v>
+        <v>4.179635950317028</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>6.550233122877124</v>
+        <v>6.561880373648549</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>7.067213743485965</v>
+        <v>6.599077426713876</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>10.57710556064414</v>
+        <v>10.10248383460019</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7.378551030851064</v>
+        <v>7.368121395152912</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.2139</t>
+          <t>X ≈ -0.2138</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>135</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.4146440664716593</v>
+        <v>0.427166356147282</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2452180333595706</v>
+        <v>0.2581278429356217</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.809863555560248</v>
+        <v>2.822870686977851</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.05179546341077</v>
+        <v>-4.436367720043762</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.636347213960732</v>
+        <v>-1.623236409585793</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.8837276337934767</v>
+        <v>0.8967705300878421</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4568081708365739</v>
+        <v>0.06782911424796367</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.465184838787359</v>
+        <v>1.478001306687439</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.295847810298682</v>
+        <v>-2.281931056756662</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5500453071668261</v>
+        <v>0.5633104701927039</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.721597703898745</v>
+        <v>3.322609835087917</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.557948472521332</v>
+        <v>5.571504518872935</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5.066929064056879</v>
+        <v>5.056499428358727</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>123</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.243777073597386</v>
+        <v>-8.231254783921763</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-7.460210257884796</v>
+        <v>-7.447300448308745</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.348704241643368</v>
+        <v>-1.335697110225766</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.038970669727533</v>
+        <v>2.051949812125997</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.305088750048256</v>
+        <v>2.318199554423195</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.268589046160685</v>
+        <v>-2.255546149866319</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7357753379585787</v>
+        <v>-0.7227090836581027</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.291656789007007</v>
+        <v>2.85755535952206</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.240481472374313</v>
+        <v>0.8073983754069616</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.649928263988329</v>
+        <v>1.210092914827129</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.258183069752235</v>
+        <v>2.271640363462453</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1464581631464128</v>
+        <v>-0.1330058744263027</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.5667127740911297</v>
+        <v>-0.5531567277395268</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.569023962139859</v>
+        <v>-3.579453597838011</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-7.308253135024792</v>
+        <v>-6.892680736416708</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.216123044285347</v>
+        <v>-4.827396241245069</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-10.79617693606729</v>
+        <v>-10.36922644952969</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.258516396052379</v>
+        <v>-2.886060129470742</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.574715388902156</v>
+        <v>-1.218467329625263</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>1.284789052951176</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.584229390681003</v>
+        <v>-3.211686012197688</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.051412789462326</v>
+        <v>-3.678754655984086</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.371671934904064</v>
+        <v>-3.739736812507033</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.962537860672732</v>
+        <v>-5.32494972648395</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.685809703508831</v>
+        <v>-4.05906264945002</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.169945064681748</v>
+        <v>-2.554096261800417</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.330940416367554</v>
+        <v>-3.709541232761048</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.821959824832014</v>
+        <v>-4.219099700181744</v>
       </c>
     </row>
     <row r="23">
@@ -1456,101 +1456,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.858401823859609</v>
+        <v>-3.21621014818141</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-5.199902444122969</v>
+        <v>-5.562690358892297</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.594771150719723</v>
+        <v>-5.957461743647507</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-9.844080061907682</v>
+        <v>-10.23900130594133</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-10.38250127698002</v>
+        <v>-10.77729085903702</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-14.46462138305998</v>
+        <v>-14.89168153528446</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-16.00920911493079</v>
+        <v>-16.44698012984441</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-9.907049448018867</v>
+        <v>-10.29640171480779</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-12.15783035609898</v>
+        <v>-11.82797210662468</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-12.2780285338278</v>
+        <v>-11.94259678530765</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-12.48278185814521</v>
+        <v>-12.14729794356767</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-14.63817972269759</v>
+        <v>-14.31880214415352</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-15.0584343336425</v>
+        <v>-14.73895299746693</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-15.53864000866581</v>
+        <v>-15.24851146488763</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.1549</t>
+          <t>X ≈ -0.1548</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>147</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.288874604960085</v>
+        <v>3.301396894635708</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.67730099199553</v>
+        <v>1.690210801571581</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.438656149974904</v>
+        <v>-1.425649018557301</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.092957526850277</v>
+        <v>2.105936669248742</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.166552123596034</v>
+        <v>-1.153441319221095</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4914340318066905</v>
+        <v>0.5044769281010559</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.808060858752107</v>
+        <v>3.821127113052583</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.101299410777692</v>
+        <v>-2.088118401482454</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.842571405803525</v>
+        <v>-2.829372666848762</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.413785026205453</v>
+        <v>-6.400379898552622</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.2171778063055</v>
+        <v>-3.203720512595282</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-5.223610975490679</v>
+        <v>-5.210158686770569</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.004409804122659</v>
+        <v>-6.990853757771056</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.754688471846215</v>
+        <v>-6.765118107544367</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>174</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.068150963888272</v>
+        <v>-3.055628674212649</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.642114503607502</v>
+        <v>1.655024313183553</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.971383728045396</v>
+        <v>2.984390859462998</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.496064288772516</v>
+        <v>-1.483085146374052</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>7.160916795005889</v>
+        <v>7.174027599380828</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.584795514330743</v>
+        <v>4.597838410625108</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.247064639723149</v>
+        <v>-1.233998385422673</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.009889892529834299</v>
+        <v>0.0230709018250721</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6258226373306215</v>
+        <v>-0.6126238983758583</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.475947822358549</v>
+        <v>-1.462542694705718</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.70368965242325</v>
+        <v>-5.690232358713033</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-7.968157069790472</v>
+        <v>-7.954704781070362</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-9.288115635815409</v>
+        <v>-9.298545271513561</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>176</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7888928656643941</v>
+        <v>-0.7763705759887713</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.809557387719686</v>
+        <v>-5.796647578143634</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.204426094316275</v>
+        <v>-6.191418962898673</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-6.074172961708776</v>
+        <v>-6.061193819310311</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-6.612594176780817</v>
+        <v>-6.599483372405878</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.610606784519696</v>
+        <v>-4.597563888225331</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.104431410883024</v>
+        <v>-8.091365156582548</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-9.139796627846337</v>
+        <v>-9.126615618551099</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-9.200796514028639</v>
+        <v>-9.187597775073876</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-10.61910351723839</v>
+        <v>-10.60569838958556</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-10.82385684155597</v>
+        <v>-10.81039954784575</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-13.63038277511962</v>
+        <v>-13.61693048639951</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-14.05063738606452</v>
+        <v>-14.03708133971292</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-10.96000696287915</v>
+        <v>-10.9704365985773</v>
       </c>
     </row>
     <row r="27">
@@ -1667,98 +1667,98 @@
         <v>196</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.47303015694456</v>
+        <v>-1.460507867268937</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.064195606643615</v>
+        <v>-2.051285797067564</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.499880639770709</v>
+        <v>-4.486873508353106</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.41044383369394</v>
+        <v>-6.397464691295475</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.397844640602955</v>
+        <v>-4.384733836228015</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.100402702887294</v>
+        <v>-4.087359806592929</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.631911655675658</v>
+        <v>-3.618730646380421</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.652095215327456</v>
+        <v>-1.638896476372693</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-2.488815272702439</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.706973724672729</v>
+        <v>-2.693516430962511</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.162386485694761</v>
+        <v>-2.14893419697465</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.562232933374368</v>
+        <v>-1.548676887022765</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.238508807065195</v>
+        <v>1.228079171367042</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.0959</t>
+          <t>X ≈ -0.09585</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>188</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.089183001061159</v>
+        <v>-4.076660711385536</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.636926826791132</v>
+        <v>-4.624017017215081</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-5.031795533387964</v>
+        <v>-5.018788401970362</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-9.15686154971651</v>
+        <v>-9.143882407318046</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-9.695282764788679</v>
+        <v>-9.68217196041374</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-9.92975572069016</v>
+        <v>-9.916712824395795</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.759170289026152</v>
+        <v>-5.746104034725676</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.098694113339697</v>
+        <v>-4.085513104044459</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6.287353573989833</v>
+        <v>-6.27415483503507</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.60556386540086</v>
+        <v>-6.592158737748029</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.746487402484519</v>
+        <v>-5.733030108774301</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.132358856083862</v>
+        <v>-6.118802809732259</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-6.946467311041623</v>
+        <v>-6.956896946739775</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-7.127584661673389</v>
+        <v>-6.849848069369301</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.373304616101173</v>
+        <v>-3.121228337190523</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.768173322697649</v>
+        <v>-3.515999721945398</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.17450555594381</v>
+        <v>-1.929463898745496</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.249512136869633</v>
+        <v>-1.011442772229486</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.854509223544113</v>
+        <v>-4.597563888225352</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.939242940816555</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-6.382036095695454</v>
+        <v>-6.120216677686031</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.955231103829085</v>
+        <v>-5.695761941005031</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.805356288857013</v>
+        <v>-6.545680737334834</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.010109613174649</v>
+        <v>-7.235818788798966</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-6.975726455829161</v>
+        <v>-7.201440636443643</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.469151798481377</v>
+        <v>-4.708970130533757</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.682845100351429</v>
+        <v>-5.939545159918872</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.52256453380221</v>
+        <v>-1.749208713461179</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.7069536807470485</v>
+        <v>-0.9213704162811069</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3544882922680088</v>
+        <v>0.1472728331101436</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.941052104487163</v>
+        <v>1.740912610844958</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.509990469808308</v>
+        <v>-1.724206210543478</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2416747456848825</v>
+        <v>-0.4512224248108296</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.782719142568752</v>
+        <v>-1.999347418223337</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.191650114165846</v>
+        <v>-4.4176355742052</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.194397573163677</v>
+        <v>-6.429837242923099</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.64646450576442</v>
+        <v>-3.865121892911553</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.763839189305244</v>
+        <v>-6.50884744141559</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.214892925163753</v>
+        <v>-6.962274167109051</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-7.149710642904772</v>
+        <v>-6.894620142373675</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.181079614098365</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>250</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.506561679790018</v>
+        <v>5.51908396946564</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.294988066825766</v>
+        <v>4.307897876401817</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.100119360229186</v>
+        <v>1.113126491646788</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8303724928366805</v>
+        <v>0.8433516352351447</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.30804872223549</v>
+        <v>-5.294937917860551</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.095340501792151</v>
+        <v>-1.082274247491675</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.162523900573611</v>
+        <v>-1.149342891278373</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4235237867559505</v>
+        <v>-0.4103250478011873</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.273648971783793</v>
+        <v>-1.260243844130962</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6784022961014102</v>
+        <v>-0.6649450023911925</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.044019138755985</v>
+        <v>-1.030566850035875</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.064273749700888</v>
+        <v>-3.050717703349285</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.814552417424551</v>
+        <v>-2.824982053122703</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>226</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.258774069170556</v>
+        <v>3.271296358846179</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.532156208418741</v>
+        <v>2.545066017994792</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.3673759973973176</v>
+        <v>0.3803831288149198</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.272282374420008</v>
+        <v>-1.259303232021544</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4832699611735904</v>
+        <v>-0.4701591567986512</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.6991277287545046</v>
+        <v>0.71217062504887</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.826783392013297</v>
+        <v>2.839849646313773</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.899423002081249</v>
+        <v>5.912604011376487</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.395945239792809</v>
+        <v>5.409143978747572</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.200687311401957</v>
+        <v>7.214092439054788</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.668500358765833</v>
+        <v>5.681957652476051</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.260405640005068</v>
+        <v>5.273857928725178</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.840151029060166</v>
+        <v>4.853707075411769</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.107571476380656</v>
+        <v>1.097141840682504</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>286</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.597470770699097</v>
+        <v>6.60999306037472</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.936946108783765</v>
+        <v>3.949855918359816</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.591028451138271</v>
+        <v>4.604035582555873</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.070931933396182</v>
+        <v>5.083911075794646</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.182860368673637</v>
+        <v>4.195971173048576</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.878903704990655</v>
+        <v>5.891946601285021</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.192771386319741</v>
+        <v>7.205837640620217</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.676636938587244</v>
+        <v>5.689817947882482</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.56668600345386</v>
+        <v>4.579884742408623</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.066211168076293</v>
+        <v>4.079616295729124</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.560758543059436</v>
+        <v>4.574215836769653</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.294442399705552</v>
+        <v>5.307894688425662</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.671390585963444</v>
+        <v>7.684946632315047</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.571461568589399</v>
+        <v>7.561031932891247</v>
       </c>
     </row>
     <row r="34">
@@ -2093,7 +2093,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-60 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-60 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2182,53 +2182,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.4278</t>
+          <t>X &gt; -0.4277</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4036</v>
+        <v>4037</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.08543634441348047</v>
+        <v>-0.08585430213928902</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1277392059015057</v>
+        <v>-0.1281604095947202</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1633350504453972</v>
+        <v>-0.1637509787089542</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.31624144685685</v>
+        <v>-0.3166187131710885</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3715839509128713</v>
+        <v>-0.371952253006377</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3326641534614652</v>
+        <v>-0.3330397843935771</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2803021639241976</v>
+        <v>-0.2806916559980621</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.313439288995184</v>
+        <v>-0.3138247117087403</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1628952294681056</v>
+        <v>-0.1633186153419715</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3558271896056198</v>
+        <v>-0.3562101890951297</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3982339375968422</v>
+        <v>-0.3986083687278281</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.399541674664853</v>
+        <v>-0.3999156987608075</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3353166033050456</v>
+        <v>-0.3357102739287825</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3689627246594824</v>
+        <v>-0.3685044707596106</v>
       </c>
     </row>
     <row r="7">
@@ -2238,101 +2238,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2665162002796464</v>
+        <v>-0.2669856822756458</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1229312960413296</v>
+        <v>-0.1234532059569773</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2056311998903197</v>
+        <v>-0.2061368234353438</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.4104641605497719</v>
+        <v>-0.410917720005088</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3630654079004003</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2508658776937267</v>
+        <v>-0.2513621447634478</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2472966443288627</v>
+        <v>-0.2477949251199334</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1774790351698243</v>
+        <v>-0.1779997564665194</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.07518172741909268</v>
+        <v>-0.07572883643524619</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.238237500462148</v>
+        <v>-0.2387529441060821</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2295122985958074</v>
+        <v>-0.2300322841867128</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2310450868597869</v>
+        <v>-0.2315646050870086</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1381943885828463</v>
+        <v>-0.1387416554450951</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.173913375986757</v>
+        <v>-0.1734222827209635</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.3983</t>
+          <t>X &gt; -0.3982</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3964</v>
+        <v>3965</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2178537086937524</v>
+        <v>-0.2184725916203192</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.05571615852634437</v>
+        <v>-0.05639681809151398</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2860441617834013</v>
+        <v>-0.2866723011097605</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4441116541185295</v>
+        <v>-0.444698679230271</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3648823492176234</v>
+        <v>-0.3654965489627173</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2047658983164027</v>
+        <v>-0.2054168960281331</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2002511036556243</v>
+        <v>-0.2009046603818589</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.02639297600070023</v>
+        <v>0.02567599565187351</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.08007913589462845</v>
+        <v>0.07934749627945337</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.07566510081610289</v>
+        <v>-0.07636881263692885</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.06463874681984549</v>
+        <v>-0.06534822819764941</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.0665103137433789</v>
+        <v>-0.06721923218864134</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.08225840666733575</v>
+        <v>0.08150619982771445</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0940247773281726</v>
+        <v>0.09456397461999444</v>
       </c>
     </row>
     <row r="9">
@@ -2342,101 +2342,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2368460281207234</v>
+        <v>-0.2375700229297877</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1105914411630664</v>
+        <v>-0.1113719004744524</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2127167635658509</v>
+        <v>-0.2134776169000077</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3731799050318827</v>
+        <v>-0.3738984916040309</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2633786714740651</v>
+        <v>-0.2641335534860332</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1297740858653498</v>
+        <v>-0.1305588120833363</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.09909875471237939</v>
+        <v>-0.09989293243705077</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1079866404474714</v>
+        <v>0.1071324769288395</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.111842066902625</v>
+        <v>0.1109855948201286</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.03807082692996744</v>
+        <v>-0.03890238071637953</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.05064428898398177</v>
+        <v>-0.05147613326794698</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.02739061091465089</v>
+        <v>-0.02822826335565765</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1261636867182361</v>
+        <v>0.1252802625800271</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1613824591971209</v>
+        <v>0.1619965837032922</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.3688</t>
+          <t>X &gt; -0.3687</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3898</v>
+        <v>3899</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2561588520432636</v>
+        <v>-0.2569896501662541</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0640912170617014</v>
+        <v>-0.06499908089810447</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2148972680645045</v>
+        <v>-0.215773764107702</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3266387661193164</v>
+        <v>-0.3274848958469718</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2113504882964108</v>
+        <v>-0.212235768423497</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1303200461685705</v>
+        <v>-0.131221425978211</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.09866956709301178</v>
+        <v>-0.09958095512092768</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.06288593549196264</v>
+        <v>0.06192471435543467</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.06727816046417701</v>
+        <v>0.06631429646114384</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.0510964346234104</v>
+        <v>-0.05204502271158873</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1133164206848534</v>
+        <v>-0.1142530495464982</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.0901729849098345</v>
+        <v>-0.09111542732375</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1451645678164226</v>
+        <v>0.144154091522509</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1272638986349079</v>
+        <v>0.1279802449023819</v>
       </c>
     </row>
     <row r="11">
@@ -2446,101 +2446,101 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3861</v>
+        <v>3862</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2218843708036715</v>
+        <v>-0.2228515144053205</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.01324264983635004</v>
+        <v>0.01218285317001744</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1868641108452067</v>
+        <v>-0.1878804796932627</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.19757894090138</v>
+        <v>-0.1985905135251897</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1276869651295485</v>
+        <v>-0.1287276362795708</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.02285801222725325</v>
+        <v>-0.02392047737275504</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.01591961244361784</v>
+        <v>-0.0169860593293123</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1775329910736616</v>
+        <v>0.1764068501900837</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2343137714437731</v>
+        <v>0.2331712025220938</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1747339518901612</v>
+        <v>0.1735895754240815</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.08805733122777326</v>
+        <v>0.08693080614696669</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1629184744979639</v>
+        <v>0.1617726944775839</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.378709160708226</v>
+        <v>0.3774987087656569</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3324043295321459</v>
+        <v>0.3331743425271654</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.3393</t>
+          <t>X &gt; -0.3392</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3826</v>
+        <v>3827</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2402473850706173</v>
+        <v>-0.2413326972010239</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.0898812403536482</v>
+        <v>0.08867412021530896</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1344910124578149</v>
+        <v>-0.1356489122093976</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1725472151925231</v>
+        <v>-0.1736929308321038</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.09709696213119656</v>
+        <v>-0.09827472703677387</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.08422889623134466</v>
+        <v>0.08300977539904153</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1181215383852958</v>
+        <v>0.1168911150540097</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2654510472343219</v>
+        <v>0.2641713273493309</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.323330820396265</v>
+        <v>0.322034033618479</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.349327529521652</v>
+        <v>0.348004654955389</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2115428592916331</v>
+        <v>0.2102508200631021</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.31292965957212</v>
+        <v>0.3116112643543048</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5345765246654537</v>
+        <v>0.5331903426277336</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4856044043213501</v>
+        <v>0.4864368128296945</v>
       </c>
     </row>
     <row r="13">
@@ -2550,101 +2550,101 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1699938465948563</v>
+        <v>-0.1712047444451059</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.04414773069130717</v>
+        <v>0.04284143114060157</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1526255832959009</v>
+        <v>-0.1538903150759126</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.139464606480189</v>
+        <v>-0.1407303190595783</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1117280914864764</v>
+        <v>-0.113014638827444</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.06867817867680515</v>
+        <v>0.06735069784549097</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1297975471166524</v>
+        <v>0.128451304558844</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2819789926404894</v>
+        <v>0.2805808531339267</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3671102569168028</v>
+        <v>0.3656875771330945</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4263510282161533</v>
+        <v>0.4248916465293462</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2627927552278777</v>
+        <v>0.2613707870824769</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3647223041086747</v>
+        <v>0.3632736343021108</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.512444712242754</v>
+        <v>0.5109463303526667</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4347626510685529</v>
+        <v>0.4356974306802428</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.3098</t>
+          <t>X &gt; -0.3097</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3749</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2340018502471892</v>
+        <v>-0.2214795605715665</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.05611542657052127</v>
+        <v>0.06902523614657241</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1381785121112529</v>
+        <v>-0.1251713806936507</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2328890128829357</v>
+        <v>-0.2199098704844715</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1182669234063312</v>
+        <v>-0.1051561190313919</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1937584004681909</v>
+        <v>0.1801843151282725</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.256736175524189</v>
+        <v>0.2431783616670415</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.443334954286577</v>
+        <v>0.4298848051264272</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5303387598610243</v>
+        <v>0.5168992462851563</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5477205992260181</v>
+        <v>0.5344803764924961</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4113631623207539</v>
+        <v>0.3981680040053917</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4342000028062571</v>
+        <v>0.4476522915263672</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5357262502991063</v>
+        <v>0.5492822966507092</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4539458487797248</v>
+        <v>0.4701899927561541</v>
       </c>
     </row>
     <row r="15">
@@ -2654,101 +2654,101 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3704</v>
+        <v>3705</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.08558252252366572</v>
+        <v>-0.08715594446658059</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.012318529689054</v>
+        <v>0.01066892832540844</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1526397245622064</v>
+        <v>-0.154257792529755</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1423792572979465</v>
+        <v>-0.1439969515750832</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1006153799246974</v>
+        <v>-0.1022615581405688</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1846518361698273</v>
+        <v>0.1829370544085265</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2224714087441342</v>
+        <v>0.2207429938876828</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4439451021218019</v>
+        <v>0.4421418837148892</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4788218589707043</v>
+        <v>0.4770064885869942</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5606552353359078</v>
+        <v>0.5587909361332137</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3442035846646974</v>
+        <v>0.3423904884394346</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3398988321020795</v>
+        <v>0.3380870479948754</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4477370465204373</v>
+        <v>0.4458824045837986</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.3889033061175127</v>
+        <v>0.3901326567288024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.2803</t>
+          <t>X &gt; -0.2802</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3654</v>
+        <v>3655</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1345618544341391</v>
+        <v>-0.136314067611778</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.06847415520547173</v>
+        <v>0.06661072068870055</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1206173382701436</v>
+        <v>-0.122443612008432</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.0846930093467293</v>
+        <v>-0.08652558168164148</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.007693821880593532</v>
+        <v>-0.009566738821256138</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2228175737543339</v>
+        <v>0.220890930229352</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3715811043264381</v>
+        <v>0.3696099687836281</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.602503421830761</v>
+        <v>0.6004522466620799</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5294141744356722</v>
+        <v>0.5273798702316341</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6240000167344704</v>
+        <v>0.6219097497470969</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3527161069612035</v>
+        <v>0.3506919576962773</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3752368787494831</v>
+        <v>0.3732067348697825</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4903090136370025</v>
+        <v>0.4882319684231433</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3451629629804387</v>
+        <v>0.3465637745106207</v>
       </c>
     </row>
     <row r="17">
@@ -2758,101 +2758,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3590</v>
+        <v>3591</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.03715189223328963</v>
+        <v>-0.03918462098940978</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.05934120397179043</v>
+        <v>0.05721788750368262</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1816357078074802</v>
+        <v>-0.1837085999689947</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.09184972938554381</v>
+        <v>-0.09394356054380637</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1150506672202098</v>
+        <v>-0.117160140082774</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.08644713432397566</v>
+        <v>0.08429218290540774</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2393272769123627</v>
+        <v>0.2371254189897485</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.482637389748966</v>
+        <v>0.4803485182295475</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4927488140785812</v>
+        <v>0.4904535951354489</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5763232040647992</v>
+        <v>0.573970342238951</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3316728500160337</v>
+        <v>0.3293788707306646</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2426178322907759</v>
+        <v>0.2403488193212056</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4507359968878077</v>
+        <v>0.4483914280538244</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3821049641910008</v>
+        <v>0.3837063345130005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.2508</t>
+          <t>X &gt; -0.2507</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3516</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.1148066511067611</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.04865974247078952</v>
+        <v>0.04621987186667553</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3024898286534068</v>
+        <v>-0.3048491250246101</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2987055213477205</v>
+        <v>-0.3010612972662798</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2826230695680678</v>
+        <v>-0.2850088398463697</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.08321535675940339</v>
+        <v>-0.08564561353761491</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.01789061689046179</v>
+        <v>0.01542657567044614</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.2478708736382558</v>
+        <v>0.2453192325149303</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1457943950622749</v>
+        <v>0.1432676815371039</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1923356829476219</v>
+        <v>0.1897561558689915</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.08169962412871001</v>
+        <v>-0.08421183956084377</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.08820452402752466</v>
+        <v>-0.09071466129227446</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1616648168520101</v>
+        <v>0.1590633600570328</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.07008922080065361</v>
+        <v>0.05965958510250147</v>
       </c>
     </row>
     <row r="19">
@@ -2865,98 +2865,98 @@
         <v>3416</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.07220144739783763</v>
+        <v>-0.05967915772221488</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.02396384739186175</v>
+        <v>0.02108340732364411</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3551053916680829</v>
+        <v>-0.357897727787126</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4426202078932562</v>
+        <v>-0.445381581343959</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5564132082167959</v>
+        <v>-0.5591714945028841</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3015211870906782</v>
+        <v>-0.304339589160044</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1950482750241349</v>
+        <v>-0.1979038122009484</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.08447989948484746</v>
+        <v>0.08151625541946572</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2527635528377843</v>
+        <v>-0.2556334371609879</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1216162136674299</v>
+        <v>-0.1245713295111273</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3392565968620929</v>
+        <v>-0.3421605624965025</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3470334788203715</v>
+        <v>-0.3499349015279805</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.01907468646903254</v>
+        <v>-0.02209610545639151</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.29628543850189</v>
+        <v>-0.3067150742000422</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.2213</t>
+          <t>X &gt; -0.2212</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3300</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.04334757610834572</v>
+        <v>-0.03082528643272298</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.129712809717482</v>
+        <v>0.1426226192935331</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2349078630013182</v>
+        <v>-0.221900731583716</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6026078399923662</v>
+        <v>-0.6058921639179076</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.6871712638391259</v>
+        <v>-0.6740604594641866</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5712724426136333</v>
+        <v>-0.5582295463192679</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3369869908962286</v>
+        <v>-0.3403680447684891</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.0308254446244689</v>
+        <v>-0.03433078474083828</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3779756341211424</v>
+        <v>-0.381381662999452</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2723766300692034</v>
+        <v>-0.2758707369232596</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5814325991317162</v>
+        <v>-0.5848480620700869</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.6076555023923476</v>
+        <v>-0.5942032136722375</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3915464769736161</v>
+        <v>-0.3779904306220132</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5660675689397578</v>
+        <v>-0.57649720463791</v>
       </c>
     </row>
     <row r="21">
@@ -2969,98 +2969,98 @@
         <v>3165</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.06288276465441811</v>
+        <v>-0.05036047497879537</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1247860466237469</v>
+        <v>0.1376958561997981</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3647796296698189</v>
+        <v>-0.3517724982522168</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4554860930219107</v>
+        <v>-0.4425069506234465</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6466850858718587</v>
+        <v>-0.6335742814969194</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6333340572471045</v>
+        <v>-0.6202911609527391</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3708455522971619</v>
+        <v>-0.3577792979966858</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.09463630979369242</v>
+        <v>-0.09883784077332081</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.296170659781815</v>
+        <v>-0.3003155751140696</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3074562387664699</v>
+        <v>-0.3116651959945571</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7649741760382298</v>
+        <v>-0.7515168823280121</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7937821719313476</v>
+        <v>-0.7803298832112375</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6453164037293249</v>
+        <v>-0.631760357377722</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.80633756750359</v>
+        <v>-0.8167672032017421</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.1918</t>
+          <t>X &gt; -0.1917</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3042</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2679029026697108</v>
+        <v>0.2804251923453336</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4314772186995341</v>
+        <v>0.4443870282755853</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3249956956551117</v>
+        <v>-0.3119885642375095</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5563467708056606</v>
+        <v>-0.5433676284071964</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7660368879159662</v>
+        <v>-0.752926083541027</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5672142795888675</v>
+        <v>-0.5541713832945021</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3560900086954604</v>
+        <v>-0.3430237543949843</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2315574311455961</v>
+        <v>-0.2183764218503583</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3583035369202818</v>
+        <v>-0.3451047979655186</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3866009770435355</v>
+        <v>-0.3731958493907044</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8872122895268006</v>
+        <v>-0.8737549958165829</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8199560223851705</v>
+        <v>-0.8065037336650605</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6484946569987216</v>
+        <v>-0.6349386106471187</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6946313128881201</v>
+        <v>-0.7050609485862722</v>
       </c>
     </row>
     <row r="23">
@@ -3070,101 +3070,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.619736774389267</v>
+        <v>0.6161245751091471</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6937496767328852</v>
+        <v>0.6911050340067675</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1612820709274985</v>
+        <v>0.1586874001120222</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.430859017311235</v>
+        <v>-0.433730264283092</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.7284821587679957</v>
+        <v>-0.7311388813842967</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.6374385698655445</v>
+        <v>-0.6402342254587836</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.2061764151048067</v>
+        <v>-0.208771150451021</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.05416476744667165</v>
+        <v>-0.05643167310906705</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2183638280355851</v>
+        <v>-0.1862369542016964</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1740961682062689</v>
+        <v>-0.1414551311234362</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.7572464653480608</v>
+        <v>-0.7246834745178319</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.7572630328048362</v>
+        <v>-0.7247168844474388</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5239228725079101</v>
+        <v>-0.4910480543472246</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5493993386492377</v>
+        <v>-0.5406049024001121</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.1623</t>
+          <t>X &gt; -0.1622</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2770</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.7917602357467075</v>
+        <v>0.8042825254223303</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9852407744069893</v>
+        <v>0.9981505839830405</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4459677356804477</v>
+        <v>0.4589748670980498</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.03470462280057518</v>
+        <v>0.04768376519903939</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2510090110441539</v>
+        <v>-0.2378982066692146</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.04643292667150689</v>
+        <v>0.05947582296587228</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5754176209515691</v>
+        <v>0.5884838752520452</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4331439694624919</v>
+        <v>0.4463249787577297</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3721440832801903</v>
+        <v>0.3853428222349535</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.424545974064543</v>
+        <v>0.4379511017173741</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1773192636104426</v>
+        <v>-0.1638619699002248</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.07073394020002866</v>
+        <v>-0.05728165147991859</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1949320264723937</v>
+        <v>0.2084880728239966</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.191945777521255</v>
+        <v>0.1815161418231028</v>
       </c>
     </row>
     <row r="25">
@@ -3177,98 +3177,98 @@
         <v>2623</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6518152062864075</v>
+        <v>0.6643374959620303</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.9464558518048065</v>
+        <v>0.9593656613808577</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5515871452082166</v>
+        <v>0.5645942766258187</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.08064542557735166</v>
+        <v>-0.06766628317888745</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1996995037833358</v>
+        <v>-0.1865886994083965</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.02149386359301531</v>
+        <v>0.0345367598873807</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.394251568356573</v>
+        <v>0.4073178226570491</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5751810174591725</v>
+        <v>0.5883620267544103</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.5523054164465293</v>
+        <v>0.5655041554012925</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.8077845013385385</v>
+        <v>0.8211896289913696</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.006957385693489471</v>
+        <v>0.006499908016728284</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2180471975002121</v>
+        <v>0.2314994862203221</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.5984025751180155</v>
+        <v>0.6119586214696184</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.581253911206737</v>
+        <v>0.5708242755085848</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; -0.1328</t>
+          <t>X &gt; -0.1327</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2449</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.9161166001656937</v>
+        <v>0.9286388898413165</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8970297164786913</v>
+        <v>0.9099395260547425</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3796620307069247</v>
+        <v>0.3926691621245268</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.0199192466137319</v>
+        <v>0.03289838901219611</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7226669337503964</v>
+        <v>-0.7095561293754571</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.302726016859566</v>
+        <v>-0.2896831205652006</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5108661131527654</v>
+        <v>0.5239323674532415</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6153446171887396</v>
+        <v>0.6285256264839774</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6360107171232272</v>
+        <v>0.6492094560779904</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9700423307886368</v>
+        <v>0.9834474584414679</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.3977920689455416</v>
+        <v>0.4112493626557594</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7996721638164885</v>
+        <v>0.8131244525365986</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.114411427922633</v>
+        <v>1.127967474274236</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.282466774082138</v>
+        <v>1.272037138383986</v>
       </c>
     </row>
     <row r="27">
@@ -3281,98 +3281,98 @@
         <v>2273</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.048136690788702</v>
+        <v>1.060658980464325</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.416325506333024</v>
+        <v>1.429235315909075</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.8894726378358655</v>
+        <v>0.9024797692534676</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4917891228410767</v>
+        <v>0.5047682652395409</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2666056953987166</v>
+        <v>-0.2534948910237773</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.03083624231694415</v>
+        <v>0.04387913861130954</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.177954702783339</v>
+        <v>1.191020957083815</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.370692113504703</v>
+        <v>1.38387312279994</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.397681668589449</v>
+        <v>1.410880407544212</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.867398102567243</v>
+        <v>1.880803230220074</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.266692292547944</v>
+        <v>1.280149586258162</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.917001538762705</v>
+        <v>1.930453827482815</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.288651899221236</v>
+        <v>2.302207945572839</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.230410187062859</v>
+        <v>2.219980551364706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.1033</t>
+          <t>X &gt; -0.1032</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2077</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.286051328321555</v>
+        <v>1.298573617997178</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.744771408183496</v>
+        <v>1.757681217759547</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.398049066536345</v>
+        <v>1.411056197953947</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.143131279548278</v>
+        <v>1.156110421946742</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1232464149816508</v>
+        <v>0.1363572193565901</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4206883526973115</v>
+        <v>0.4337312489916769</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.732199218958975</v>
+        <v>1.745265473259451</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.842772199570831</v>
+        <v>1.855953208866069</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.685479583489638</v>
+        <v>1.698678322444401</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.279745346945099</v>
+        <v>2.29315047459793</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.641674738082493</v>
+        <v>1.655132031792711</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.301960639770734</v>
+        <v>2.315412928490844</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.652047868016972</v>
+        <v>2.665603914368575</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.324012820899902</v>
+        <v>2.31358318520175</v>
       </c>
     </row>
     <row r="29">
@@ -3385,46 +3385,46 @@
         <v>1889</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.821013770843493</v>
+        <v>1.833536060519116</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.379900719022693</v>
+        <v>2.392810528598744</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.037970074893018</v>
+        <v>2.05097720631062</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.168223207500517</v>
+        <v>2.181202349898982</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.100421367759218</v>
+        <v>1.113532172134157</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.450801367941793</v>
+        <v>1.463844264236158</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.477766962474696</v>
+        <v>2.490833216775172</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.434088063428511</v>
+        <v>2.447269072723749</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.478964302180032</v>
+        <v>2.492163041134795</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.164042928692602</v>
+        <v>3.177448056345433</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.376970917238971</v>
+        <v>2.390428210949189</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.152486949121197</v>
+        <v>3.165939237841307</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.526303275179998</v>
+        <v>3.539859321531601</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.246643982787148</v>
+        <v>3.236214347088996</v>
       </c>
     </row>
     <row r="30">
@@ -3434,49 +3434,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.910362154849409</v>
+        <v>2.896386405591613</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.080261225970659</v>
+        <v>3.067731506823684</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.744774942176925</v>
+        <v>2.732377828545168</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.696880806375866</v>
+        <v>2.684349852703953</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.386488094866642</v>
+        <v>1.373630115413363</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.218371837807958</v>
+        <v>2.205763503337224</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.380668999395546</v>
+        <v>3.36882498007818</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.507309828642541</v>
+        <v>3.495933401056739</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.505692365263094</v>
+        <v>3.494368951010493</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.377657441517826</v>
+        <v>4.367563642500002</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.519697466368896</v>
+        <v>3.568685419474512</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.385434542954222</v>
+        <v>4.434911462501255</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.499621737234982</v>
+        <v>4.54951996747662</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.333666109891311</v>
+        <v>4.359331672367439</v>
       </c>
     </row>
     <row r="31">
@@ -3489,46 +3489,46 @@
         <v>1478</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.528212559357009</v>
+        <v>3.540734849032631</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.608113912563248</v>
+        <v>3.621023722139299</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.077927208673017</v>
+        <v>3.09093434009062</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.802226349399604</v>
+        <v>2.815205491798068</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.790192143799693</v>
+        <v>1.803302948174633</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.561247072043095</v>
+        <v>2.57428996833746</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.100329322294492</v>
+        <v>4.113395576594968</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.580371904568473</v>
+        <v>4.593552913863711</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.857667011620272</v>
+        <v>4.870865750575035</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.496039796822387</v>
+        <v>5.509444924475218</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.952991479270707</v>
+        <v>4.966448772980925</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.00225961631844</v>
+        <v>6.01571190503855</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.1232769945481</v>
+        <v>6.136833040899702</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.831726337649826</v>
+        <v>5.821296701951674</v>
       </c>
     </row>
     <row r="32">
@@ -3541,46 +3541,46 @@
         <v>1228</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.12545418793335</v>
+        <v>3.137976477608973</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.468277969105898</v>
+        <v>3.481187778681949</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.480575386287811</v>
+        <v>3.493582517705413</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.203662395116808</v>
+        <v>3.216641537515272</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.235273753334546</v>
+        <v>3.248384557709485</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.021315039584408</v>
+        <v>4.034357935878774</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.158079693647636</v>
+        <v>5.171145947948112</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.749528216690237</v>
+        <v>5.762709225985475</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.93282800477504</v>
+        <v>5.946026743729803</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.874233764372505</v>
+        <v>6.887638892025336</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.099447866765033</v>
+        <v>6.11290516047525</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.436762620201662</v>
+        <v>7.450214908921772</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.993706706325163</v>
+        <v>8.007262752676766</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.591962240555844</v>
+        <v>7.581532604857692</v>
       </c>
     </row>
     <row r="33">
@@ -3593,46 +3593,46 @@
         <v>1002</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.095384035079448</v>
+        <v>3.107906324755071</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.679419204550314</v>
+        <v>3.692329014126365</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.1827540907681</v>
+        <v>4.195761222185702</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.213206824174009</v>
+        <v>4.226185966572473</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.073987205908224</v>
+        <v>4.087098010283164</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.770630740430271</v>
+        <v>4.783673636724636</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.683901015173952</v>
+        <v>5.696967269474428</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.715719612400441</v>
+        <v>5.728900621695679</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.053921323024525</v>
+        <v>6.067120061979288</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.800602525222146</v>
+        <v>6.814007652874977</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.196647604098182</v>
+        <v>6.210104897808399</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.927637547870759</v>
+        <v>7.941089836590869</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.704987727345021</v>
+        <v>8.718543773696624</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.054509458822906</v>
+        <v>9.044079823124754</v>
       </c>
     </row>
     <row r="34">
@@ -3645,46 +3645,46 @@
         <v>716</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.696505813868242</v>
+        <v>1.709028103543865</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.576552312635826</v>
+        <v>3.589462122211877</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.019672432854875</v>
+        <v>4.032679564272478</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.870595956523822</v>
+        <v>3.883575098922286</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.030498763798029</v>
+        <v>4.043609568172968</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.32794070151369</v>
+        <v>4.340983597808055</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.08119581105705</v>
+        <v>5.094262065357526</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.731330848029735</v>
+        <v>5.744511857324973</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.647984593132364</v>
+        <v>6.661183332087127</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.892831475143538</v>
+        <v>7.906236602796369</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.850089324010305</v>
+        <v>6.863546617720523</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.979444548394852</v>
+        <v>8.992896837114962</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.117849155327043</v>
+        <v>9.131405201678646</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.64690009654187</v>
+        <v>9.636470460843718</v>
       </c>
     </row>
     <row r="35">
@@ -3759,7 +3759,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-60 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-60 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3848,53 +3848,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.4278</t>
+          <t>X &lt; -0.4277</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.54270625810328</v>
+        <v>6.555228547778903</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.545590476464326</v>
+        <v>8.558500286040378</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.945902492759295</v>
+        <v>6.958909624176897</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.30507128801739</v>
+        <v>14.31805043041586</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>18.58592718137896</v>
+        <v>18.5990379857539</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>15.26891128776933</v>
+        <v>15.28195418406369</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.97935829338861</v>
+        <v>13.99242454768908</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>13.51217489460711</v>
+        <v>13.52535590390234</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.631897899991067</v>
+        <v>8.64509663894583</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.01068837761375</v>
+        <v>15.02409350526658</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>16.01075433040461</v>
+        <v>16.02421162411483</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.8403182106416</v>
+        <v>14.85377049936171</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>13.21524432258827</v>
+        <v>13.22880036893987</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>13.46496565486456</v>
+        <v>13.4545360191664</v>
       </c>
     </row>
     <row r="7">
@@ -3907,98 +3907,98 @@
         <v>113</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11.22337583908206</v>
+        <v>11.23589812875768</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>6.07197921726825</v>
+        <v>6.084889026844301</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.562066262884038</v>
+        <v>6.57507339430164</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.77196541319065</v>
+        <v>13.78494455558911</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.23354419811848</v>
+        <v>13.24665500249342</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.221251622559812</v>
+        <v>8.234294518854178</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.021473657499925</v>
+        <v>9.034539911800401</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.014467249868872</v>
+        <v>5.02764825916411</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.183555859261787</v>
+        <v>3.19675459821655</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.758209435295804</v>
+        <v>6.771614562948635</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.668500358765833</v>
+        <v>5.681957652476051</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.817927763898872</v>
+        <v>4.831380052618982</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.627761648529201</v>
+        <v>2.641317694880804</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.877482980805489</v>
+        <v>2.867053345107337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.3983</t>
+          <t>X &lt; -0.3982</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>155</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.861400389467441</v>
+        <v>6.873922679143064</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.669181615212864</v>
+        <v>2.682091424788915</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.790441940874338</v>
+        <v>6.80344907229194</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.79166281541732</v>
+        <v>10.80464195781578</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>9.608080310022572</v>
+        <v>9.621191114397512</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.744231925157585</v>
+        <v>4.757274821451951</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.614136803799411</v>
+        <v>-1.600955794504173</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.675136689981713</v>
+        <v>-1.66193795102695</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7005445766032565</v>
+        <v>0.7139497042560876</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1493700380369063</v>
+        <v>-0.1359127443266885</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.7601481710140519</v>
+        <v>-0.7466958822939418</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.761047943249274</v>
+        <v>-3.747491896897671</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.801649191618154</v>
+        <v>-4.812078827316306</v>
       </c>
     </row>
     <row r="9">
@@ -4011,98 +4011,98 @@
         <v>188</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.017199977662365</v>
+        <v>6.029722267337988</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.341796577464073</v>
+        <v>3.354706387040125</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.010757658101518</v>
+        <v>4.02376478951912</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.332500152411143</v>
+        <v>7.345479294809607</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.730249150104939</v>
+        <v>5.743359954479878</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.304286832501447</v>
+        <v>2.317329728795812</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.219553115229168</v>
+        <v>2.232619369529644</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.03486432610552</v>
+        <v>-3.021683316810282</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.032034425053787</v>
+        <v>-2.018835686099024</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2225851419966105</v>
+        <v>-0.2091800143437794</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.4273384663141897</v>
+        <v>-0.4138811726039719</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.4567850962028</v>
+        <v>-1.44333280748269</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.004699281615785</v>
+        <v>-3.991143235264182</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.35072263019056</v>
+        <v>-5.361152265888713</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.3688</t>
+          <t>X &lt; -0.3687</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>221</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.425113715989127</v>
+        <v>5.43763600566475</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.003585351893641</v>
+        <v>2.016495161469692</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.41867139642828</v>
+        <v>3.431678527845882</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.358879280166995</v>
+        <v>5.37185842256546</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.915480689529218</v>
+        <v>3.928591493904158</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.950479188330846</v>
+        <v>1.963522084625211</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.865745471058567</v>
+        <v>1.878811725359043</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.768858742202568</v>
+        <v>-1.75567773290733</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9248812528192616</v>
+        <v>-0.9116825138644984</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.03494831328403336</v>
+        <v>0.04835344093686444</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7351723645320618</v>
+        <v>0.7486296582422796</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1354218536881149</v>
+        <v>-0.1219695649680048</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.72309727911265</v>
+        <v>-3.709541232761048</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.925864634619167</v>
+        <v>-3.936294270317319</v>
       </c>
     </row>
     <row r="11">
@@ -4115,98 +4115,98 @@
         <v>258</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.095708966611731</v>
+        <v>4.108231256287354</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5461508575234362</v>
+        <v>0.5590606670994873</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.476863546275688</v>
+        <v>2.48987067769329</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.607116678883187</v>
+        <v>2.620095821281652</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.068695463811018</v>
+        <v>2.081806268185957</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.04055600617783739</v>
+        <v>0.05359890247220278</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.343419188130369</v>
+        <v>0.356485442430845</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.22453940444958</v>
+        <v>-3.211358395154342</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.285539290631881</v>
+        <v>-3.272340551677118</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.360470677210188</v>
+        <v>-3.347065549557357</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.402433303853364</v>
+        <v>-2.388976010143146</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.918437743407146</v>
+        <v>-3.904985454687036</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.3393</t>
+          <t>X &lt; -0.3392</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>293</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.820554853851462</v>
+        <v>3.833077143527085</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5213941857339606</v>
+        <v>-0.5084843761579094</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.472815605962964</v>
+        <v>1.485822737380566</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.944365666898115</v>
+        <v>1.957344809296579</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.405944451825945</v>
+        <v>1.419055256200885</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.368285965407196</v>
+        <v>-1.355243069112831</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.453019682679475</v>
+        <v>-1.439953428378999</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.96798465142686</v>
+        <v>-3.954803642131623</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.028984537609162</v>
+        <v>-4.015785798654399</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.220406650964726</v>
+        <v>-5.207001523311895</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.718675333644079</v>
+        <v>-3.705218039933861</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.390776817936874</v>
+        <v>-5.377324529216764</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.858812998847647</v>
+        <v>-7.845256952496044</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.609091666571359</v>
+        <v>-7.619521302269511</v>
       </c>
     </row>
     <row r="13">
@@ -4219,98 +4219,98 @@
         <v>323</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.614920812916964</v>
+        <v>2.627443102592586</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.07455463029326381</v>
+        <v>0.08746443986931496</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.537271063015559</v>
+        <v>1.550278194433162</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.357926672403238</v>
+        <v>1.370905814801702</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.438700503770697</v>
+        <v>1.451811308145636</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.050235267491971</v>
+        <v>-1.037192371197605</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.444566507984057</v>
+        <v>-1.431500253683581</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.769335046084443</v>
+        <v>-3.756154036789205</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4.139932455486559</v>
+        <v>-4.126733716531795</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.609252686954115</v>
+        <v>-5.595847559301284</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.956420871952808</v>
+        <v>-3.94296357824259</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.470025330706456</v>
+        <v>-5.456573041986346</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.8190725113108</v>
+        <v>-6.805516464959197</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.259753655814691</v>
+        <v>-6.270183291512843</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.3098</t>
+          <t>X &lt; -0.3097</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.911967085195428</v>
+        <v>2.775148659492601</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.05095787912017613</v>
+        <v>-0.183746328449935</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.175795035904848</v>
+        <v>1.038732960649476</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.116858979323162</v>
+        <v>1.977583441165066</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.308167493980726</v>
+        <v>1.169752109093629</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.178174352087403</v>
+        <v>-2.036916987955927</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.533178339629949</v>
+        <v>-2.391169126197831</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.892253630303344</v>
+        <v>-4.745030222814762</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.075554158313281</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-5.925472954643141</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.927050944750071</v>
+        <v>-4.782465218024626</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.433208327945174</v>
+        <v>-5.556712402596531</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.123733209160356</v>
+        <v>-6.246405034885676</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.603741606613788</v>
+        <v>-5.751127605683408</v>
       </c>
     </row>
     <row r="15">
@@ -4323,98 +4323,98 @@
         <v>415</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.241501438826177</v>
+        <v>1.254023728501799</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3528193921269747</v>
+        <v>0.3657292017030258</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.162769962638812</v>
+        <v>1.175777094056414</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.052059239824629</v>
+        <v>1.065038382223094</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9955657355958394</v>
+        <v>1.008676539970779</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.839522447170438</v>
+        <v>-1.826479550876073</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.924256164442717</v>
+        <v>-1.911189910142241</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.3191504065977</v>
+        <v>-4.305969397302462</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.139186437358319</v>
+        <v>-4.125987698403556</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.471239333229626</v>
+        <v>-5.457834205576795</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.748281814173708</v>
+        <v>-3.734824520463491</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.95486251224996</v>
+        <v>-3.94141022352985</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.616080978616559</v>
+        <v>-4.602524932264956</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.366359646340271</v>
+        <v>-4.376789282038423</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.2803</t>
+          <t>X &lt; -0.2802</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>465</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.485056303445937</v>
+        <v>1.49757859312156</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1265173095183201</v>
+        <v>-0.1136074999422689</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7689365645302573</v>
+        <v>0.7819436959478594</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4690821702560299</v>
+        <v>0.4820613126544941</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1457147186247241</v>
+        <v>0.1588255229996633</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.922434741509079</v>
+        <v>-1.909391845214714</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.867383512544798</v>
+        <v>-2.854317258244322</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.054997018853179</v>
+        <v>-5.041816009557941</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.040728087831177</v>
+        <v>-4.027529348876413</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.320960799740824</v>
+        <v>-5.307555672087993</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.375176489649803</v>
+        <v>-3.361719195939585</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.770900859186092</v>
+        <v>-3.757448570465982</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.406209233571857</v>
+        <v>-4.392653187220255</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.511326610972986</v>
+        <v>-3.521756246671139</v>
       </c>
     </row>
     <row r="17">
@@ -4427,98 +4427,98 @@
         <v>529</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6256543073892686</v>
+        <v>0.6381765970648914</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04073972145400262</v>
+        <v>-0.02782991187795147</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.076678906542973</v>
+        <v>1.089686037960576</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4507883718536903</v>
+        <v>0.4637675142521545</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.8575467409025066</v>
+        <v>0.8706575452774459</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7353704896237971</v>
+        <v>-0.7223275933294317</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.576247874192866</v>
+        <v>-1.56318161989239</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.555718607567933</v>
+        <v>-3.542537598272695</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.23864666010185</v>
+        <v>-3.225447921147087</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.27780776195398</v>
+        <v>-4.264402634301149</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.781237834853783</v>
+        <v>-2.767780541143566</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.368782843859954</v>
+        <v>-2.355330555139844</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.545181122101646</v>
+        <v>-3.531625075750043</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.295459789825358</v>
+        <v>-3.30588942552351</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.2508</t>
+          <t>X &lt; -0.2507</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9833828718430055</v>
+        <v>0.9959051615186283</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.03406091450789006</v>
+        <v>0.04697072408394121</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.625947174798718</v>
+        <v>1.63895430621632</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.590637393498923</v>
+        <v>1.603616535897388</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.714467834055903</v>
+        <v>1.727578638430842</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3562806326987129</v>
+        <v>0.3693235289930783</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.05957891238813318</v>
+        <v>-0.04651265808765714</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.68570270852063</v>
+        <v>-1.672521699225392</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7533251112592296</v>
+        <v>-0.7401263723044664</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.437887382379863</v>
+        <v>-1.424482254727032</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.01298843237540126</v>
+        <v>0.02644572608561901</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1181913241864478</v>
+        <v>-0.1047390354663378</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.366260504667771</v>
+        <v>-1.352704458316168</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.024834341139361</v>
+        <v>-0.9614058941823558</v>
       </c>
     </row>
     <row r="19">
@@ -4528,101 +4528,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6315616797900248</v>
+        <v>0.5687293595365688</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1563517031894008</v>
+        <v>0.169261512765452</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.608073905683717</v>
+        <v>1.62108103710132</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.022417947382138</v>
+        <v>2.035397089780602</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.762405823219048</v>
+        <v>2.775516627593987</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.355302306389262</v>
+        <v>1.368345202683628</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9864776800260699</v>
+        <v>0.999543934326546</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.310567122334994</v>
+        <v>1.323765861289758</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3183964827616208</v>
+        <v>0.3318016104144519</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.250006794807675</v>
+        <v>1.263464088517892</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.142344497607645</v>
+        <v>1.155796786327755</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2722282951554291</v>
+        <v>-0.2586722488038262</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.911194382006407</v>
+        <v>0.961381583240879</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.2213</t>
+          <t>X &lt; -0.2212</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.4121306870539456</v>
+        <v>0.3606801000581541</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2868301149924122</v>
+        <v>-0.3390754892156167</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8399251854718912</v>
+        <v>0.7858537643740533</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.305129774390075</v>
+        <v>2.318108916788539</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.807625639854429</v>
+        <v>2.750693150100616</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.202045283606694</v>
+        <v>2.146057010923982</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.387384559035148</v>
+        <v>1.400450813335624</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.0530348494787134</v>
+        <v>-0.0398538401834756</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.589128281370613</v>
+        <v>1.602327020325376</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.860657597559225</v>
+        <v>0.8740627252120561</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.99410378662364</v>
+        <v>2.007561080333858</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.977661738223311</v>
+        <v>1.920284731472634</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.262555518591789</v>
+        <v>1.205555134653146</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.827205824333646</v>
+        <v>1.867700873706511</v>
       </c>
     </row>
     <row r="21">
@@ -4632,101 +4632,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4111259951427257</v>
+        <v>0.3688249021081305</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2109309362895004</v>
+        <v>-0.253927849739263</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.113424973534784</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.405606623950106</v>
+        <v>1.36060735249086</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.175284611097837</v>
+        <v>2.128995484844964</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.010873924552115</v>
+        <v>1.964936111774541</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.254555114074272</v>
+        <v>1.209279454281045</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1610669136226335</v>
+        <v>0.1742479229178713</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.039524229945556</v>
+        <v>1.052722968900319</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8157038465877662</v>
+        <v>0.8291089742405973</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.237794151129506</v>
+        <v>2.190169820155774</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.228784208524345</v>
+        <v>2.181136389253567</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.869757663911678</v>
+        <v>1.822085643931047</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.285657226181272</v>
+        <v>2.318473444259446</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.1918</t>
+          <t>X &lt; -0.1917</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5668328156228242</v>
+        <v>-0.6019059480412281</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.028795220593885</v>
+        <v>-1.064579187818367</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8310017131703589</v>
+        <v>0.7931999535384264</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.47213882218351</v>
+        <v>1.433792811705729</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.182190688445907</v>
+        <v>2.142780573399797</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.518425473544681</v>
+        <v>1.479784178072876</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.024216693779849</v>
+        <v>0.9859285174853269</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5161464595371967</v>
+        <v>0.477963381784356</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.061134253909522</v>
+        <v>1.022361932808266</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9106248487526969</v>
+        <v>0.871364288955867</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.240116222417093</v>
+        <v>2.199439826470957</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.958019786174503</v>
+        <v>1.917581298112275</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.591755934900227</v>
+        <v>1.551321221581205</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.617016756205857</v>
+        <v>1.645518874521031</v>
       </c>
     </row>
     <row r="23">
@@ -4736,101 +4736,101 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.309764850822219</v>
+        <v>-1.299171939254805</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.490632848206907</v>
+        <v>-1.481987931102253</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4524562734584734</v>
+        <v>-0.4460571818226029</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.949521429006893</v>
+        <v>0.9538091515750153</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.766807952621186</v>
+        <v>1.769003210512302</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.454966985971971</v>
+        <v>1.458082592952934</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5138473571086308</v>
+        <v>0.5183809531635717</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.009889892529834299</v>
+        <v>0.01459153495113696</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5694096561364432</v>
+        <v>0.491069537924858</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2585878703214277</v>
+        <v>0.1794934300890247</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.58168000842533</v>
+        <v>1.500050889145363</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.498979213797554</v>
+        <v>1.417459465753588</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.043887833151544</v>
+        <v>0.9624510209305512</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.011190156832818</v>
+        <v>0.9885270078327579</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.1623</t>
+          <t>X &lt; -0.1622</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.465538173367101</v>
+        <v>-1.490453814833693</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.864012667928087</v>
+        <v>-1.889458951792022</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9704688750649382</v>
+        <v>-0.9967926854288933</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1385752628660484</v>
+        <v>-0.1654718941766262</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.5411412630369696</v>
+        <v>0.5134506031107549</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1522427462000024</v>
+        <v>-0.1793017380045541</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.155517492942543</v>
+        <v>-1.181905787653754</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.9927822031566365</v>
+        <v>-1.019549380953883</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.7183539196953461</v>
+        <v>-0.7453803983546621</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.010825616277558</v>
+        <v>-1.038087271014319</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1565089465021288</v>
+        <v>0.1282552932481238</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1374314259506519</v>
+        <v>-0.1654780926394253</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5901996756268133</v>
+        <v>-0.6181492355476621</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.669556123873825</v>
+        <v>-0.6472042753449756</v>
       </c>
     </row>
     <row r="25">
@@ -4840,101 +4840,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.002384642277569</v>
+        <v>-1.023962388150245</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.51880503662251</v>
+        <v>-1.540743608024947</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.01613810493339</v>
+        <v>-1.038597646284259</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.07924367477558292</v>
+        <v>0.05609217936254396</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.374343304342581</v>
+        <v>0.3507460130823361</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.08933018877515053</v>
+        <v>-0.1125140543384191</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6700577339943763</v>
+        <v>-0.6929125453639742</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.101272236126206</v>
+        <v>-1.124060123480639</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.9263885435846859</v>
+        <v>-0.9493396949383026</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.540315638450508</v>
+        <v>-1.563241845463452</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1743329165150342</v>
+        <v>-0.1982783357245381</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6365425032419694</v>
+        <v>-0.6601865965335421</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.220051972813785</v>
+        <v>-1.243508090532202</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.267493593895189</v>
+        <v>-1.247961345039919</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; -0.1328</t>
+          <t>X &lt; -0.1327</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.215957630964581</v>
+        <v>-1.2338851516745</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.191813360047</v>
+        <v>-1.210343359486473</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6033904553567879</v>
+        <v>-0.6224264215517934</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.08391322144903768</v>
+        <v>-0.1032277817785356</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.077657055012871</v>
+        <v>1.057443034520404</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.3953526910463125</v>
+        <v>0.3756344441152137</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7299260712613957</v>
+        <v>-0.7490203738325221</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.9859129220533234</v>
+        <v>-1.005037584182368</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8951655778006966</v>
+        <v>-0.9143823270374227</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.53362507692124</v>
+        <v>-1.552781157563842</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7494124574881482</v>
+        <v>-0.7691266033469972</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.399521531100483</v>
+        <v>-1.418851368864324</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.786954779024654</v>
+        <v>-1.806220095693782</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.103175171915616</v>
+        <v>-2.086262723380088</v>
       </c>
     </row>
     <row r="27">
@@ -4944,101 +4944,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.175525463835584</v>
+        <v>-1.190593449889185</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.629231524132251</v>
+        <v>-1.644549676045735</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.134237128731513</v>
+        <v>-1.149952087470552</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6519550933702192</v>
+        <v>-0.6679030766657732</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.3480159677914614</v>
+        <v>0.331355185587725</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.07986244795024788</v>
+        <v>-0.09621617933058957</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.430364786735446</v>
+        <v>-1.446028292799085</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.76079603880256</v>
+        <v>-1.776434094732238</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.684896017982275</v>
+        <v>-1.700605825338947</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.397973296108169</v>
+        <v>-2.41356637249406</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.708364437799631</v>
+        <v>-1.724404461850661</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.564365459102305</v>
+        <v>-2.579944892220844</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.95555691158502</v>
+        <v>-2.971064023695604</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.947596837792965</v>
+        <v>-2.932832621612192</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.1033</t>
+          <t>X &lt; -0.1032</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.203900607314601</v>
+        <v>-1.216324590845637</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.670737347000909</v>
+        <v>-1.683342999510593</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.455555262274473</v>
+        <v>-1.468373021498309</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.201986181627255</v>
+        <v>-1.214904575188626</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1055133736250582</v>
+        <v>-0.1191094578215655</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.464265321105195</v>
+        <v>-0.4776223962703199</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.742680667726717</v>
+        <v>-1.755444979198948</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.939867650573611</v>
+        <v>-1.952661583323277</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.681755345134029</v>
+        <v>-1.694700047801149</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.407959822223724</v>
+        <v>-2.420771445498858</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.804074667739556</v>
+        <v>-1.817242167591594</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.525819530145412</v>
+        <v>-2.538635309693582</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.82188510555013</v>
+        <v>-2.834670736617383</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.545796295975045</v>
+        <v>-2.533645782931863</v>
       </c>
     </row>
     <row r="29">
@@ -5048,49 +5048,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.445734352309834</v>
+        <v>-1.455960593814211</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.919463315868256</v>
+        <v>-1.929819466442595</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.755570064134943</v>
+        <v>-1.766088494972308</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.869627507163322</v>
+        <v>-1.88007540626419</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9107284899889549</v>
+        <v>-0.9217236321462607</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.259400350203478</v>
+        <v>-1.270185594344262</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.080230980111288</v>
+        <v>-2.090674604953655</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.121378998963593</v>
+        <v>-2.131908827800494</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.06916137064853</v>
+        <v>-2.079734707908479</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.761204925230572</v>
+        <v>-2.771653240104165</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.135992981278314</v>
+        <v>-2.14677132289254</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.839001217609031</v>
+        <v>-2.849465193072156</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.100849276370546</v>
+        <v>-3.111291180051794</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.916794569890968</v>
+        <v>-2.906380529142474</v>
       </c>
     </row>
     <row r="30">
@@ -5100,49 +5100,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.921542895373378</v>
+        <v>-1.909487459105783</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.041260400685466</v>
+        <v>-2.030035974149435</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.924246952117514</v>
+        <v>-1.91334409658851</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.895189879351456</v>
+        <v>-1.884233162476342</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9391452852469442</v>
+        <v>-0.9292797003625921</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.561077517225513</v>
+        <v>-1.550529123399293</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.320238126689731</v>
+        <v>-2.309115491354149</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.479197395043087</v>
+        <v>-2.468213132784726</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.3956549342969</v>
+        <v>-2.384772222248323</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.101119246486583</v>
+        <v>-3.090149620452188</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.545834617676483</v>
+        <v>-2.576420412227264</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.186981797762961</v>
+        <v>-3.217036714734519</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.215997887631929</v>
+        <v>-3.24628784280786</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.149665353769571</v>
+        <v>-3.162774420787919</v>
       </c>
     </row>
     <row r="31">
@@ -5152,49 +5152,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.890574718099948</v>
+        <v>-1.89711188740818</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.937654224919427</v>
+        <v>-1.944400541081222</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.747241122425422</v>
+        <v>-1.754118137075423</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.597088842508477</v>
+        <v>-1.604008847419458</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9835204203487038</v>
+        <v>-0.9907508186527068</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.458473904187628</v>
+        <v>-1.46548841652735</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.278422072789084</v>
+        <v>-2.285143254664156</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.61246723264766</v>
+        <v>-2.619131410915827</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.691399826060525</v>
+        <v>-2.698046997177798</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.143592261008799</v>
+        <v>-3.150190934078104</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.874468861910799</v>
+        <v>-2.88120209123808</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.500924170916413</v>
+        <v>-3.507420102683376</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.522714325022612</v>
+        <v>-3.529264808911151</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.404329017197419</v>
+        <v>-3.396972969095508</v>
       </c>
     </row>
     <row r="32">
@@ -5204,49 +5204,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.253768898722377</v>
+        <v>-1.258885049467231</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.40091272545807</v>
+        <v>-1.406151710375042</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.501948179398667</v>
+        <v>-1.507197311315672</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.38789706938325</v>
+        <v>-1.393174898190082</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.35632458430446</v>
+        <v>-1.361673526271446</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.730303231570538</v>
+        <v>-1.735494922708227</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.176361895856978</v>
+        <v>-2.181411881158411</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.487342678619861</v>
+        <v>-2.492338060360495</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.495623234269729</v>
+        <v>-2.50062535846736</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.98211183879593</v>
+        <v>-2.987039424241502</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.684760278133204</v>
+        <v>-2.689815468712446</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.288609529353984</v>
+        <v>-3.293455585350323</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.483084261457456</v>
+        <v>-3.487910928375207</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.353327927628683</v>
+        <v>-3.347527004713349</v>
       </c>
     </row>
     <row r="33">
@@ -5256,49 +5256,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9279431125422448</v>
+        <v>-0.9318901602053842</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.116836797348093</v>
+        <v>-1.120856117208412</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.366888312405095</v>
+        <v>-1.370862003079971</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.379541162423962</v>
+        <v>-1.383502584713703</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.293205472075542</v>
+        <v>-1.297240444243663</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.554606784519827</v>
+        <v>-1.55853637702905</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.814418606785708</v>
+        <v>-1.818274247491637</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.880423356225222</v>
+        <v>-1.884298076937782</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.924356586243427</v>
+        <v>-1.928224503452761</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.24474797851245</v>
+        <v>-2.248584651305897</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.079684347383477</v>
+        <v>-2.083592871663868</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.669155400378301</v>
+        <v>-2.672874542343571</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.879796520707949</v>
+        <v>-2.883484615821232</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.02988767568575</v>
+        <v>-3.025366915213837</v>
       </c>
     </row>
     <row r="34">
@@ -5308,49 +5308,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2978879689219198</v>
+        <v>-0.3006409354216828</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6935917281961963</v>
+        <v>-0.6963175802726482</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8677775349084982</v>
+        <v>-0.8704752653078245</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.8390092827273463</v>
+        <v>-0.8417098761884105</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.8341917468544864</v>
+        <v>-0.8369244399818569</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.9313338440331762</v>
+        <v>-0.9340234427389547</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.05897686542847</v>
+        <v>-1.061635138725876</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.246419471122159</v>
+        <v>-1.249049636146403</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.379627073140888</v>
+        <v>-1.382222965078945</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.7149756521478</v>
+        <v>-1.717520839436169</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.522089906201245</v>
+        <v>-1.524704321440218</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.000259961076104</v>
+        <v>-2.002733614569053</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.993298426551647</v>
+        <v>-1.995798466932257</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.138913275491021</v>
+        <v>-2.135910372746721</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3705</v>
+        <v>3706</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.09967823414220334</v>
+        <v>-0.1012440757077826</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2712750485898923</v>
+        <v>-0.2728444581866682</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4094608335275467</v>
+        <v>-0.4110058731635533</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.5338266996263101</v>
+        <v>-0.5353351247218043</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4653992876636011</v>
+        <v>-0.4669433014406366</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.5842130328365513</v>
+        <v>-0.5857168230666048</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4388749845507292</v>
+        <v>-0.4404212983938649</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.7567033670246985</v>
+        <v>-0.7581790981749279</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.587405188373161</v>
+        <v>-0.5889291976259869</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.9644551189933352</v>
+        <v>-0.9659042214895024</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.7767841731240708</v>
+        <v>-0.7782909177322637</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.105092783212413</v>
+        <v>-1.106510755105994</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.132703323365213</v>
+        <v>-1.134127468658164</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.299842565872645</v>
+        <v>-1.298160682372618</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_60.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_60.xlsx
@@ -568,1463 +568,1463 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.4204</t>
+          <t>X ≈ -0.4199</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24.10726037140642</v>
+        <v>24.82861771098217</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.7568859088084778</v>
+        <v>-2.47337864323579</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.497585015246415</v>
+        <v>6.784270713871194</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.27858529962281</v>
+        <v>13.35077093370769</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.558938530995555</v>
+        <v>-0.008498178951626301</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.2424498509914</v>
+        <v>-9.394270261855681</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.674598343620502</v>
+        <v>-6.236788339058855</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-18.45551123356132</v>
+        <v>-19.58743759578773</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.8623934179837</v>
+        <v>-13.18537802269184</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.04458287813332</v>
+        <v>-14.01181733536391</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-22.91475406060236</v>
+        <v>-23.88943070071416</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-22.88601011045873</v>
+        <v>-20.61293713997458</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-26.64415208273255</v>
+        <v>-24.23801442321543</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-26.42498205312124</v>
+        <v>-27.22072522903996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.4056</t>
+          <t>X ≈ -0.4052</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-4.846852454855835</v>
+        <v>-3.661829400631746</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.453895536590018</v>
+        <v>-2.922006005446789</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.396795771303843</v>
+        <v>8.280150958538854</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.778165692562595</v>
+        <v>1.452096723014662</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1335541147548369</v>
+        <v>-1.355799693864384</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.588812412274891</v>
+        <v>-5.725400994722179</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.674459203368905</v>
+        <v>-3.465782163828393</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-19.40596064097577</v>
+        <v>-17.86407215943282</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.71567310343064</v>
+        <v>-10.93734203845753</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-15.56858821256288</v>
+        <v>-16.40975070467577</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.77699137934453</v>
+        <v>-11.97012002945855</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-15.74655040370621</v>
+        <v>-14.23936326088335</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-20.93118799250979</v>
+        <v>-19.28791145547755</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-25.47260110074288</v>
+        <v>-21.36926236332248</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.3909</t>
+          <t>X ≈ -0.3904</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.057015284404628</v>
+        <v>-2.502650787640469</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.493967543415891</v>
+        <v>2.149925199737289</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.007929825738678</v>
+        <v>-10.70800846945899</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.880648307908082</v>
+        <v>-7.464327415212637</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-12.44305104030563</v>
+        <v>-11.07194656171102</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-9.124871019390163</v>
+        <v>-7.683427413989378</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-12.23660509307825</v>
+        <v>-10.86532488405955</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.679987167409294</v>
+        <v>-8.212556380342782</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.690379881353692</v>
+        <v>-5.130493645941833</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.540550943291919</v>
+        <v>-2.833101432225206</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.718229357398428</v>
+        <v>-3.037795585083956</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.713052245863359</v>
+        <v>-6.103822020896111</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.134239701447456</v>
+        <v>-6.500366106592658</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.94013356827427</v>
+        <v>-9.377983293556092</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.3761</t>
+          <t>X ≈ -0.3757</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.056888358736721</v>
+        <v>5.048119567038768</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.59039079526859</v>
+        <v>-2.570545040033402</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.05781565469995087</v>
+        <v>0.05763388157496507</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.857735153929873</v>
+        <v>-5.858291250121226</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.395935491632443</v>
+        <v>-6.347568899473956</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.05226997644358988</v>
+        <v>-0.02838696021530041</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1367535250308265</v>
+        <v>-0.08885328864217712</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.448498121585445</v>
+        <v>5.497668636449696</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.388967179719323</v>
+        <v>5.462127263121488</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.513920684112648</v>
+        <v>1.61315285968999</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.365711641583822</v>
+        <v>7.46554443136035</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.401985443056738</v>
+        <v>4.496865537945091</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.104691223685272</v>
+        <v>-4.985574468253951</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.181078552937855</v>
+        <v>1.322774282200101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.3614</t>
+          <t>X ≈ -0.3609</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.820272901753647</v>
+        <v>-5.271090862947247</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.121124199035442</v>
+        <v>-9.619277243988492</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.12722955893409</v>
+        <v>-4.474961438803973</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.78127150467735</v>
+        <v>-15.42928926704563</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-8.928679183013628</v>
+        <v>-10.37835730754669</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-11.33112043987723</v>
+        <v>-12.88063165781261</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-8.720702240180316</v>
+        <v>-10.17164072279895</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-11.88753497735892</v>
+        <v>-13.41257761141582</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-17.34993897941438</v>
+        <v>-19.0013624498426</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-23.60341848217076</v>
+        <v>-25.37920212866576</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-21.11349766274081</v>
+        <v>-22.81413444844038</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-26.48716749210175</v>
+        <v>-25.53817097160661</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-24.21197865964094</v>
+        <v>-23.16267616373704</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-21.28984691798762</v>
+        <v>-20.14187218244371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.3466</t>
+          <t>X ≈ -0.3463</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.797933815856489</v>
+        <v>3.034418100497739</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.35159083203915</v>
+        <v>-6.849606635183726</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.899029301428172</v>
+        <v>-4.474735681766731</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.920963341138147</v>
+        <v>-1.575774287800868</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.45853574119964</v>
+        <v>-2.064083127171514</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-11.71597983044955</v>
+        <v>-10.10814075521583</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-14.65549881261362</v>
+        <v>-12.94401964071018</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.420011838051167</v>
+        <v>-7.865305183022443</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.483344643359793</v>
+        <v>-7.904250495528863</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-18.89745354932786</v>
+        <v>-17.05405711536224</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-13.39723185834033</v>
+        <v>-11.71137447067311</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-16.2220046460426</v>
+        <v>-14.4326018963604</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.64626937095268</v>
+        <v>-14.83140119150774</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-16.42498205312405</v>
+        <v>-14.58631662688942</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.3318</t>
+          <t>X ≈ -0.3315</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-9.117193917675252</v>
+        <v>-13.75430955166274</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.889564800770081</v>
+        <v>3.958986458804212</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.173104643928923</v>
+        <v>0.3502453357251696</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.345660827507579</v>
+        <v>-5.954886268044383</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.767306775269098</v>
+        <v>-0.007933613862022071</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.064927024427007</v>
+        <v>0.264691416374113</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.346243536608959</v>
+        <v>-3.015628359937182</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.812727652786258</v>
+        <v>-3.481314115203539</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.203049457215073</v>
+        <v>-6.74071797792854</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.383325578589059</v>
+        <v>-10.78792521481082</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.259833005687689</v>
+        <v>-7.7716652618358</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.227122692039423</v>
+        <v>-7.715567678694988</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.348540829574716</v>
+        <v>1.562210679698339</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.908351280213608</v>
+        <v>5.037339287089068</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.3171</t>
+          <t>X ≈ -0.3167</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.755467873431861</v>
+        <v>6.16374416974773</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.002222839013108</v>
+        <v>-1.913126515802631</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.396958752556756</v>
+        <v>-2.306807442517623</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.043522562021863</v>
+        <v>6.494781809454352</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7267977787309121</v>
+        <v>-0.4976501566375333</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.745424952011703</v>
+        <v>-8.902348440648083</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-8.832209884996246</v>
+        <v>-8.965164046245071</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-11.38067989728086</v>
+        <v>-11.60287615832635</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-11.4445738322643</v>
+        <v>-11.64284560239028</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.134444783300196</v>
+        <v>-8.125721500891551</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-10.42306184300136</v>
+        <v>-10.5042793432293</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.227051072650745</v>
+        <v>-6.103435840897973</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.48325237071726</v>
+        <v>-2.153496820917788</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.25831538645798</v>
+        <v>-1.905157206599576</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.3024</t>
+          <t>X ≈ -0.3021</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>44</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-11.53213859850283</v>
+        <v>-11.56133582923543</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.982891610633267</v>
+        <v>4.981755392411316</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.324036706868846</v>
+        <v>2.323906360517846</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.612122701377245</v>
+        <v>-6.612664927757343</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3488913031341454</v>
+        <v>-0.3004770641035037</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.05160884472048366</v>
+        <v>-0.02771138335974399</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.132338307633923</v>
+        <v>2.180258621046804</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6022169260149326</v>
+        <v>-0.5530647809231368</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.876050775186989</v>
+        <v>3.949209576985716</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.512579247800261</v>
+        <v>-1.41335916594484</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.094888348820199</v>
+        <v>5.194716892399548</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>9.673543820711167</v>
+        <v>9.797180327231906</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>9.256023208193369</v>
+        <v>9.404674702177523</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>7.383380342807541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.2876</t>
+          <t>X ≈ -0.2873</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.506302857447373</v>
+        <v>3.3135327740086</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.07867609343117</v>
+        <v>-4.161239238586184</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.479874388638528</v>
+        <v>-2.604521280064667</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.345154090785627</v>
+        <v>-4.429238827553107</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.87825285038236</v>
+        <v>-6.885290033275986</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.591491268094103</v>
+        <v>-3.584997471541122</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-10.66143287100583</v>
+        <v>-11.47468280261066</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-11.13034564772557</v>
+        <v>-11.94257771286758</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.20528770963611</v>
+        <v>-4.15037749739669</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.05519433904189</v>
+        <v>-4.974480939583636</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.2644469142353643</v>
+        <v>-1.261774338837093</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.229162062560249</v>
+        <v>-3.163791925462675</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.649870712072001</v>
+        <v>-3.559764272726376</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.575017946879065</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.2729</t>
+          <t>X ≈ -0.2725</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>64</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.586186611688326</v>
+        <v>-4.288776088139933</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5936367201793615</v>
+        <v>1.764157196358717</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.315096571841345</v>
+        <v>6.034198582125413</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3296925760373668</v>
+        <v>4.613324683836993</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.027431760086778</v>
+        <v>6.489396250162336</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.885361268359091</v>
+        <v>11.4478824288942</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7.803235254874565</v>
+        <v>10.66898202598178</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.339397384181503</v>
+        <v>9.468761195661791</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.59929008695687</v>
+        <v>4.057881682744672</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.311759942900238</v>
+        <v>4.089617517194753</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.546555946656966</v>
+        <v>3.207583021779428</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.827781340103236</v>
+        <v>7.951418937763599</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.723659788208053</v>
+        <v>2.87230779329979</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.737482053123465</v>
+        <v>-1.565483293556092</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.2581</t>
+          <t>X ≈ -0.2579</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>75</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.505976150911863</v>
+        <v>2.088692880998124</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5728048605666132</v>
+        <v>-0.8693696851290156</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.495359214638057</v>
+        <v>4.063658877571349</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9.615735937005788</v>
+        <v>7.582597399546962</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>7.751586904834475</v>
+        <v>7.08662187831569</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>8.050976080154271</v>
+        <v>7.36082347719325</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>10.63036719379866</v>
+        <v>9.962490178719293</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>11.49852143253072</v>
+        <v>12.15260784882224</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>16.76652922462603</v>
+        <v>17.44523710139504</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>18.58593139926236</v>
+        <v>19.2748808109635</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>19.71851136919675</v>
+        <v>19.07144840345657</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>15.76060479048119</v>
+        <v>15.88425331820056</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>14.01209125574354</v>
+        <v>14.16074679629393</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15.57501794687725</v>
+        <v>14.41368337311058</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.2433</t>
+          <t>X ≈ -0.2431</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.997961825122864</v>
+        <v>-1.57607310221082</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9048815006566997</v>
+        <v>-0.2530278219995878</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.507291145343103</v>
+        <v>0.8639344107398799</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.628919606827367</v>
+        <v>3.935483844794874</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>9.080387443220097</v>
+        <v>8.341643151082458</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.384940593724473</v>
+        <v>6.65529497587211</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7.302792625357213</v>
+        <v>6.593021694758335</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5.840828930095988</v>
+        <v>5.140614255841534</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>13.76972989626378</v>
+        <v>13.92513390946501</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>10.92718305645374</v>
+        <v>10.15263210429157</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>8.727316535921304</v>
+        <v>8.968924809741054</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>8.764248745159527</v>
+        <v>9.027630611068425</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.347470701995483</v>
+        <v>6.241289916319502</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>12.57501794687747</v>
+        <v>12.37446768683606</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.2286</t>
+          <t>X ≈ -0.2283</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8805220478542353</v>
+        <v>-0.8843091395393543</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.436497622854382</v>
+        <v>-2.044627109555961</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.226777792194646</v>
+        <v>-4.104788455535115</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.120867750501269</v>
+        <v>3.527042057699035</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.709221474224009</v>
+        <v>2.201053257379478</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.918391950714287</v>
+        <v>5.807658727536932</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.854957976358513</v>
+        <v>1.57887611762979</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.377164811704105</v>
+        <v>1.106960632185832</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.321686780657359</v>
+        <v>0.2393310887425812</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.179635950317028</v>
+        <v>1.907230001844738</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>6.561880373648549</v>
+        <v>4.203332863311054</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.599077426713876</v>
+        <v>5.095319552014473</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>10.10248383460019</v>
+        <v>8.027412233722991</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7.368121395152912</v>
+        <v>5.41368337311058</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.2138</t>
+          <t>X ≈ -0.2137</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.427166356147282</v>
+        <v>1.446722707487112</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2581278429356217</v>
+        <v>-0.1364543776689047</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.822870686977851</v>
+        <v>3.066929936174994</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.436367720043762</v>
+        <v>-4.716855087358688</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.623236409585793</v>
+        <v>-0.8895574657206851</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.8967705300878421</v>
+        <v>1.541501434393204</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.06782911424796367</v>
+        <v>1.480845345167744</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.478001306687439</v>
+        <v>1.734437045216062</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.281931056756662</v>
+        <v>-1.899657866079004</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5633104701927039</v>
+        <v>0.8736358552642827</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.322609835087917</v>
+        <v>3.547193249454807</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.605359986819543</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.571504518872935</v>
+        <v>5.368475441550849</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5.056499428358727</v>
+        <v>4.898095843134556</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.1991</t>
+          <t>X ≈ -0.1989</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.231254783921763</v>
+        <v>-8.155273115209567</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-7.447300448308745</v>
+        <v>-6.512643748752332</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.335697110225766</v>
+        <v>-1.261220446744815</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.051949812125997</v>
+        <v>2.900921658986178</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.318199554423195</v>
+        <v>1.605220905131034</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.255546149866319</v>
+        <v>-2.960703253469404</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7227090836581027</v>
+        <v>-1.408456116888416</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.85755535952206</v>
+        <v>2.964420800147607</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.8073983754069616</v>
+        <v>0.508093352301124</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.210092914827129</v>
+        <v>0.4907163843895574</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.271640363462453</v>
+        <v>1.093027549756513</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1330058744263027</v>
+        <v>-2.07461216449132</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.5531567277395268</v>
+        <v>-2.469770091055331</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.579453597838011</v>
+        <v>-5.446531680652868</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ -0.1844</t>
+          <t>X ≈ -0.1842</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>136</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.892680736416708</v>
+        <v>-7.657170648416397</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.827396241245069</v>
+        <v>-5.563877145336953</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-10.36922644952969</v>
+        <v>-11.1046739571809</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.886060129470742</v>
+        <v>-3.621848739495803</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.218467329625263</v>
+        <v>-1.169921409859491</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.284789052951176</v>
+        <v>1.308746461900618</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.211686012197688</v>
+        <v>-3.163674333207197</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.678754655984086</v>
+        <v>-3.629507093590369</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.739736812507033</v>
+        <v>-3.666479702727166</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.32494972648395</v>
+        <v>-5.225602401189711</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.05906264945002</v>
+        <v>-3.959154613431345</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.554096261800417</v>
+        <v>-2.430399640772343</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.709541232761048</v>
+        <v>-3.56085168498322</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.219099700181744</v>
+        <v>-4.047100940614911</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ -0.1696</t>
+          <t>X ≈ -0.1694</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.21621014818141</v>
+        <v>-2.869824055102811</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-5.562690358892297</v>
+        <v>-4.453001140258664</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.957461743647507</v>
+        <v>-5.566163589005185</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-10.23900130594133</v>
+        <v>-10.47225077081193</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-10.77729085903702</v>
+        <v>-11.6809243721955</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-14.89168153528446</v>
+        <v>-15.00526115553485</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-16.44698012984441</v>
+        <v>-16.50476616562361</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-10.29640171480779</v>
+        <v>-10.49577878212223</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-11.82797210662468</v>
+        <v>-11.25217585169068</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-11.94259678530765</v>
+        <v>-11.35657997207368</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-12.14729794356767</v>
+        <v>-11.5607204196101</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-14.31880214415352</v>
+        <v>-14.38025152397166</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-14.73895299746693</v>
+        <v>-14.77540945053548</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-15.24851146488763</v>
+        <v>-15.96521350938343</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.1548</t>
+          <t>X ≈ -0.1547</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>147</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.301396894635708</v>
+        <v>2.591928991439694</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.690210801571581</v>
+        <v>0.3284797974401599</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.425649018557301</v>
+        <v>-1.425802408561466</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.105936669248742</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.153441319221095</v>
+        <v>-0.4246232906117839</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.5044769281010559</v>
+        <v>0.528434337050669</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.821127113052583</v>
+        <v>3.869138792042904</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.088118401482454</v>
+        <v>-1.358598730245198</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.829372666848762</v>
+        <v>-3.436387665912605</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.400379898552622</v>
+        <v>-6.301032573258205</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.203720512595282</v>
+        <v>-3.78408458541999</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-5.210158686770569</v>
+        <v>-4.406189956898785</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-6.990853757771056</v>
+        <v>-6.161892101149689</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.765118107544367</v>
+        <v>-5.232575130290783</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ -0.1401</t>
+          <t>X ≈ -0.1399</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.055628674212649</v>
+        <v>-3.091507173724331</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.655024313183553</v>
+        <v>1.720664578329256</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.984390859462998</v>
+        <v>2.489717287688968</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.483085146374052</v>
+        <v>-2.03156146179402</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>7.174027599380828</v>
+        <v>6.781514978649405</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.597838410625108</v>
+        <v>4.728719102119499</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.233998385422673</v>
+        <v>-1.145890475478062</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.0230709018250721</v>
+        <v>-1.030327887024193</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6126238983758583</v>
+        <v>-0.4859051473237841</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.462542694705718</v>
+        <v>-1.891129076975972</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.690232358713033</v>
+        <v>-5.583641617535314</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-7.954704781070362</v>
+        <v>-8.432451624356467</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-7.083423504408671</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-9.298545271513561</v>
+        <v>-9.74135538657935</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ -0.1254</t>
+          <t>X ≈ -0.1253</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>176</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7763705759887713</v>
+        <v>0.3307972660222305</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.796647578143634</v>
+        <v>-5.79783436458829</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.191418962898673</v>
+        <v>-5.623390534721175</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-6.061193819310311</v>
+        <v>-4.925324675324553</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-6.599483372405878</v>
+        <v>-5.982755634458286</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.597563888225331</v>
+        <v>-4.573606479275718</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.091365156582548</v>
+        <v>-8.043353477592227</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-9.126615618551099</v>
+        <v>-8.50918623797557</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-9.187597775073876</v>
+        <v>-8.546158847112366</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-10.60569838958556</v>
+        <v>-9.938169246109162</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-10.81039954784575</v>
+        <v>-10.14230969364538</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-13.61693048639951</v>
+        <v>-12.92505204718945</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-14.03708133971292</v>
+        <v>-13.88839179193509</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-10.9704365985773</v>
+        <v>-10.23025602082882</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ -0.1106</t>
+          <t>X ≈ -0.1105</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.460507867268937</v>
+        <v>-1.994647907361212</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.051285797067564</v>
+        <v>-1.515969322413966</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.486873508353106</v>
+        <v>-4.487026898357421</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.397464691295475</v>
+        <v>-6.934462444771846</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.384733836228015</v>
+        <v>-4.330928080569123</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-4.087359806592929</v>
+        <v>-4.058142561750195</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.618730646380421</v>
+        <v>-3.553703576307342</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.638896476372693</v>
+        <v>-2.044284432866938</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.488815272702439</v>
+        <v>-2.868113013681793</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.693516430962511</v>
+        <v>-3.072253461217656</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.14893419697465</v>
+        <v>-2.498622806327219</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.548676887022765</v>
+        <v>-1.347388980313724</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.228079171367042</v>
+        <v>0.9635115518047286</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.09585</t>
+          <t>X ≈ -0.09575</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>188</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.076660711385536</v>
+        <v>-4.105856505738167</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.624017017215081</v>
+        <v>-4.625203803659737</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-5.018788401970362</v>
+        <v>-5.018941791974683</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-9.143882407318046</v>
+        <v>-9.144376899696049</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-9.68217196041374</v>
+        <v>-9.633626040647968</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-9.916712824395795</v>
+        <v>-9.892755415446182</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.746104034725676</v>
+        <v>-5.698092355735355</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.085513104044459</v>
+        <v>-4.036265541650742</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6.27415483503507</v>
+        <v>-6.200897725255373</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.592158737748029</v>
+        <v>-6.492811412453456</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.733030108774301</v>
+        <v>-5.633122072755626</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.118802809732259</v>
+        <v>-5.970113261954431</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-6.956896946739775</v>
+        <v>-6.784898187173113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ -0.08113</t>
+          <t>X ≈ -0.08103</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-6.849848069369301</v>
+        <v>-6.616392018123697</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.121228337190523</v>
+        <v>-3.368651228883522</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.515999721945398</v>
+        <v>-3.762389217198177</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.929463898745496</v>
+        <v>-2.183229813664603</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.011442772229486</v>
+        <v>-1.223203592297729</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.597563888225352</v>
+        <v>-4.815152372995549</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.875808462221123</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-6.120216677686031</v>
+        <v>-6.307824797483576</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.695761941005031</v>
+        <v>-5.861705619180867</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.545680737334834</v>
+        <v>-6.202442412556245</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.235818788798966</v>
+        <v>-6.88967464753194</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-7.201440636443643</v>
+        <v>-6.831507910166998</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.708970130533757</v>
+        <v>-4.328115112093201</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.939545159918872</v>
+        <v>-5.528345612396727</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.06637</t>
+          <t>X ≈ -0.0663</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.749208713461179</v>
+        <v>-2.019915746455617</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.9213704162811069</v>
+        <v>-0.6619163610232306</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1472728331101436</v>
+        <v>0.4149338859562448</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.740912610844958</v>
+        <v>2.015406162464984</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.724206210543478</v>
+        <v>-1.415019449075118</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4512224248108296</v>
+        <v>-0.1618417733935047</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.999347418223337</v>
+        <v>-1.693086097913074</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.4176355742052</v>
+        <v>-4.119703172021914</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.429837242923099</v>
+        <v>-6.117460094884201</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.865121892911553</v>
+        <v>-4.000112205110938</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.50884744141559</v>
+        <v>-6.655233044803893</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.962274167109051</v>
+        <v>-7.087262385870439</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.894620142373675</v>
+        <v>-6.992224234002826</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.181079614098365</v>
+        <v>-6.252983293556035</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.05162</t>
+          <t>X ≈ -0.05156</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.51908396946564</v>
+        <v>5.258812477901863</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.307897876401817</v>
+        <v>4.074041767248005</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.113126491646788</v>
+        <v>0.891459157419348</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8433516352351447</v>
+        <v>0.622936824132033</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.294937917860551</v>
+        <v>-5.44400155984777</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.772809666526847</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.082274247491675</v>
+        <v>-1.247808385234386</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.149342891278373</v>
+        <v>-1.315234771115733</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4103250478011873</v>
+        <v>-0.5553946312485465</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.260243844130962</v>
+        <v>-1.379223212063529</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6649450023911925</v>
+        <v>-0.7865509105956363</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.030566850035875</v>
+        <v>-1.126790547732782</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.050717703349285</v>
+        <v>-3.115573972304531</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.824982053122703</v>
+        <v>-2.866529110289164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ -0.03687</t>
+          <t>X ≈ -0.03683</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.271296358846179</v>
+        <v>2.996496104628434</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.545066017994792</v>
+        <v>2.734904922556282</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.3803831288149198</v>
+        <v>1.019581031157934</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.259303232021544</v>
+        <v>-1.053178099433559</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4701591567986512</v>
+        <v>-0.2208413373018274</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.71217062504887</v>
+        <v>0.9330014502395656</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.839849646313773</v>
+        <v>3.074988532820278</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.912604011376487</v>
+        <v>6.133384847326795</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.409143978747572</v>
+        <v>5.655883603828762</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.214092439054788</v>
+        <v>7.475226829181189</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.681957652476051</v>
+        <v>5.949500478561397</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.273857928725178</v>
+        <v>5.567138581565104</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.853707075411769</v>
+        <v>5.171980655001171</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.097141840682504</v>
+        <v>1.015739173404206</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ -0.02212</t>
+          <t>X ≈ -0.0221</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.60999306037472</v>
+        <v>6.996930428634123</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.949855918359816</v>
+        <v>4.005302639252939</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.604035582555873</v>
+        <v>4.315790003050864</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.083911075794646</v>
+        <v>5.149899396378245</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.195971173048576</v>
+        <v>4.308537579370004</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.891946601285021</v>
+        <v>5.989773802414284</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.205837640620217</v>
+        <v>7.337568417414175</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.689817947882482</v>
+        <v>5.815397628861838</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.579884742408623</v>
+        <v>4.72208699155599</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.079616295729124</v>
+        <v>4.250371086797365</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.574215836769653</v>
+        <v>4.750455991373968</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.307894688425662</v>
+        <v>5.512848080851519</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.684946632315047</v>
+        <v>7.93459156273844</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.561031932891247</v>
+        <v>8.183636424753821</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ -0.007375</t>
+          <t>X ≈ -0.007365</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2182,1509 +2182,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.4277</t>
+          <t>X &gt; -0.4273</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4037</v>
+        <v>4048</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.08585430213928902</v>
+        <v>-0.08460086699484037</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1281604095947202</v>
+        <v>-0.1277716686635273</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1637509787089542</v>
+        <v>-0.163301842925172</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3166187131710885</v>
+        <v>-0.3157431528550347</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.371952253006377</v>
+        <v>-0.372642922423104</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3330397843935771</v>
+        <v>-0.3329753155677651</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2806916559980621</v>
+        <v>-0.2816115204125254</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3138247117087403</v>
+        <v>-0.314698190256145</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1633186153419715</v>
+        <v>-0.1654419819395372</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3562101890951297</v>
+        <v>-0.3587247518078058</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3986083687278281</v>
+        <v>-0.4010280796778858</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3999156987608075</v>
+        <v>-0.4031665253039307</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3357102739287825</v>
+        <v>-0.3400128431486422</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3685044707596106</v>
+        <v>-0.3735366532398814</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.413</t>
+          <t>X &gt; -0.4125</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4007</v>
+        <v>4017</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2669856822756458</v>
+        <v>-0.2768612045395926</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1234532059569773</v>
+        <v>-0.1096701460815552</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2061368234353438</v>
+        <v>-0.216917663005006</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.410917720005088</v>
+        <v>-0.4212104012203426</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3630654079004003</v>
+        <v>-0.3754531009263715</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2513621447634478</v>
+        <v>-0.2630474730646739</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2477949251199334</v>
+        <v>-0.2356542186007147</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1779997564665194</v>
+        <v>-0.1659665692525394</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.07572883643524619</v>
+        <v>-0.06496450689265743</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2387529441060821</v>
+        <v>-0.253361079890901</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2300322841867128</v>
+        <v>-0.2197633345317271</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2315646050870086</v>
+        <v>-0.2472036452803366</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1387416554450951</v>
+        <v>-0.1555871401409021</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1734222827209635</v>
+        <v>-0.1663514787689309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.3982</t>
+          <t>X &gt; -0.3978</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3965</v>
+        <v>3974</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2184725916203192</v>
+        <v>-0.2402347243101062</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.05639681809151398</v>
+        <v>-0.07923973794047612</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2866723011097605</v>
+        <v>-0.3088587678682089</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.444698679230271</v>
+        <v>-0.4414802065404473</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3654965489627173</v>
+        <v>-0.3648454251598139</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2054168960281331</v>
+        <v>-0.2039429935902675</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2009046603818589</v>
+        <v>-0.2007031613171861</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.02567599565187351</v>
+        <v>0.02553281181886291</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07934749627945337</v>
+        <v>0.05267822935728361</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.07636881263692885</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.06534822819764941</v>
+        <v>-0.09262057210549557</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.06721923218864134</v>
+        <v>-0.09580383061729236</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.08150619982771445</v>
+        <v>0.05143096392539093</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.09456397461999444</v>
+        <v>0.06307105974033789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.3835</t>
+          <t>X &gt; -0.3831</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3932</v>
+        <v>3942</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2375700229297877</v>
+        <v>-0.2218690941663795</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1113719004744524</v>
+        <v>-0.09733544519711046</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2134776169000077</v>
+        <v>-0.2244415201637651</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3738984916040309</v>
+        <v>-0.3844707923655335</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2641335534860332</v>
+        <v>-0.2779283180137853</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1305588120833363</v>
+        <v>-0.1432267324404108</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.09989293243705077</v>
+        <v>-0.1141308895952662</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1071324769288395</v>
+        <v>0.09240720404341118</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1109855948201286</v>
+        <v>0.09475369866463978</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.03890238071637953</v>
+        <v>-0.05618288477662503</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.05147613326794698</v>
+        <v>-0.06871250502905468</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.02822826335565765</v>
+        <v>-0.04703250081290378</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1252802625800271</v>
+        <v>0.1046165312152496</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1619965837032922</v>
+        <v>0.1397107703708471</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.3687</t>
+          <t>X &gt; -0.3683</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3899</v>
+        <v>3909</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2569896501662541</v>
+        <v>-0.2663586377375751</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.06499908089810447</v>
+        <v>-0.07645646933893602</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.215773764107702</v>
+        <v>-0.2268228167248836</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3274848958469718</v>
+        <v>-0.3382604891918533</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.212235768423497</v>
+        <v>-0.226688067517955</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.131221425978211</v>
+        <v>-0.1441962163195072</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.09958095512092768</v>
+        <v>-0.1143442845380847</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.06192471435543467</v>
+        <v>0.04677568005532606</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.06631429646114384</v>
+        <v>0.04944202620951188</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.05204502271158873</v>
+        <v>-0.07027551193635873</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1142530495464982</v>
+        <v>-0.1323171299717103</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.09111542732375</v>
+        <v>-0.0853923461132311</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.144154091522509</v>
+        <v>0.1475882127149859</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1279802449023819</v>
+        <v>0.1297232810154156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.354</t>
+          <t>X &gt; -0.3536</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3862</v>
+        <v>3873</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2228515144053205</v>
+        <v>-0.219839050826252</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.01218285317001744</v>
+        <v>0.01224519549126768</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1878804796932627</v>
+        <v>-0.1873358581927675</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1985905135251897</v>
+        <v>-0.1979875648430962</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1287276362795708</v>
+        <v>-0.1323270831025027</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.02392047737275504</v>
+        <v>-0.02580951972934287</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.0169860593293123</v>
+        <v>-0.02086050664564709</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1764068501900837</v>
+        <v>0.1718819848559932</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2331712025220938</v>
+        <v>0.2265215410914863</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1735895754240815</v>
+        <v>0.1649739996056567</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.08693080614696669</v>
+        <v>0.07851308522706546</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1617726944775839</v>
+        <v>0.151194287121406</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3774987087656569</v>
+        <v>0.3642599187703084</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3331743425271654</v>
+        <v>0.3181501946959102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.3392</t>
+          <t>X &gt; -0.3389</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3827</v>
+        <v>3837</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2413326972010239</v>
+        <v>-0.2503715651467218</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.08867412021530896</v>
+        <v>0.0766253534022141</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1356489122093976</v>
+        <v>-0.1471100584407026</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1736929308321038</v>
+        <v>-0.1850607152140853</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.09827472703677387</v>
+        <v>-0.1142027105232799</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.08300977539904153</v>
+        <v>0.06878623853949506</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1168911150540097</v>
+        <v>0.1003888362853687</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2641713273493309</v>
+        <v>0.2472895266969175</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.322034033618479</v>
+        <v>0.3028071270488226</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.348004654955389</v>
+        <v>0.3265286308641606</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2102508200631021</v>
+        <v>0.1891297002941457</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3116112643543048</v>
+        <v>0.2880242747693913</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5331903426277336</v>
+        <v>0.5068306250434418</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4864368128296945</v>
+        <v>0.4579888200743483</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.3245</t>
+          <t>X &gt; -0.3241</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3797</v>
+        <v>3806</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1712047444451059</v>
+        <v>-0.140381528998013</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.04284143114060157</v>
+        <v>0.04500338959048378</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1538903150759126</v>
+        <v>-0.151161035114157</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1407303190595783</v>
+        <v>-0.1380652890086864</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.113014638827444</v>
+        <v>-0.1150682759453758</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.06735069784549097</v>
+        <v>0.06719058417458967</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.128451304558844</v>
+        <v>0.1257689027811395</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2805808531339267</v>
+        <v>0.2776591307166001</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3656875771330945</v>
+        <v>0.3601768796117071</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4248916465293462</v>
+        <v>0.417056237069076</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2613707870824769</v>
+        <v>0.2539706471743415</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3632736343021108</v>
+        <v>0.353213804605808</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5109463303526667</v>
+        <v>0.4982345184500829</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4356974306802428</v>
+        <v>0.4206898541054969</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.3097</t>
+          <t>X &gt; -0.3094</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3749</v>
+        <v>3760</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2214795605715665</v>
+        <v>-0.2175064710571348</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.06902523614657241</v>
+        <v>0.06895923417773275</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1251713806936507</v>
+        <v>-0.1247887652363531</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2199098704844715</v>
+        <v>-0.2192118226601067</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1051561190313919</v>
+        <v>-0.1103877529369157</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1801843151282725</v>
+        <v>0.1769243062867787</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2431783616670415</v>
+        <v>0.2369877633277326</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4298848051264272</v>
+        <v>0.4230061049974481</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5168992462851563</v>
+        <v>0.5070223674234313</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5344803764924961</v>
+        <v>0.5215689434377424</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3981680040053917</v>
+        <v>0.3855875353548157</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4476522915263672</v>
+        <v>0.4322047311199526</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5492822966507092</v>
+        <v>0.5306759124955462</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.4701899927561541</v>
+        <v>0.4491443660183734</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.295</t>
+          <t>X &gt; -0.2947</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3705</v>
+        <v>3716</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.08715594446658059</v>
+        <v>-0.08318771654695212</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.01066892832540844</v>
+        <v>0.0107883431760456</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.154257792529755</v>
+        <v>-0.1537830024627169</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1439969515750832</v>
+        <v>-0.1435089333640107</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1022615581405688</v>
+        <v>-0.108136964537735</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1829370544085265</v>
+        <v>0.179347333828332</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2207429938876828</v>
+        <v>0.21397809762815</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4421418837148892</v>
+        <v>0.4345634567144856</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4770064885869942</v>
+        <v>0.4662644994953453</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5587909361332137</v>
+        <v>0.5444798252495886</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3423904884394346</v>
+        <v>0.3286441306965813</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3380870479948754</v>
+        <v>0.3213169684103363</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4458824045837986</v>
+        <v>0.4256016534142759</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.3901326567288024</v>
+        <v>0.3670382349692076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.2802</t>
+          <t>X &gt; -0.2799</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3655</v>
+        <v>3665</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.136314067611778</v>
+        <v>-0.1304544955424092</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.06661072068870055</v>
+        <v>0.06884384294954771</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.122443612008432</v>
+        <v>-0.1196799595820366</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.08652558168164148</v>
+        <v>-0.0838712186017645</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.009566738821256138</v>
+        <v>-0.0138300596248655</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.220890930229352</v>
+        <v>0.2317297581322535</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3696099687836281</v>
+        <v>0.3766306776860517</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6004522466620799</v>
+        <v>0.6067965261957085</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5273798702316341</v>
+        <v>0.5305069938586513</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6219097497470969</v>
+        <v>0.6212784607220314</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3506919576962773</v>
+        <v>0.3507754654704485</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3732067348697825</v>
+        <v>0.3698137088162028</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.4882319684231433</v>
+        <v>0.481059678580209</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3465637745106207</v>
+        <v>0.3363755058982036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.2655</t>
+          <t>X &gt; -0.2652</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3591</v>
+        <v>3601</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.03918462098940978</v>
+        <v>-0.05654930755955689</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.05721788750368262</v>
+        <v>0.03871330848183874</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1837085999689947</v>
+        <v>-0.2290518636834733</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.09394356054380637</v>
+        <v>-0.1673537339464062</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.117160140082774</v>
+        <v>-0.1294108660193132</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.08429218290540774</v>
+        <v>0.03238686145666492</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2371254189897485</v>
+        <v>0.1937063549171114</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.4803485182295475</v>
+        <v>0.4492942382629579</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.4904535951354489</v>
+        <v>0.4678155247976363</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.573970342238951</v>
+        <v>0.5596362225620055</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3293788707306646</v>
+        <v>0.3000018793544399</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2403488193212056</v>
+        <v>0.2350670454858488</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4483914280538244</v>
+        <v>0.4385604063385955</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3837063345130005</v>
+        <v>0.3701769397124437</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.2507</t>
+          <t>X &gt; -0.2505</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3516</v>
+        <v>3526</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1148066511067611</v>
+        <v>-0.1021798135555372</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.04621987186667553</v>
+        <v>0.0580287436834368</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3048491250246101</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3010612972662798</v>
+        <v>-0.3321995464852705</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2850088398463697</v>
+        <v>-0.2828999346027246</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.08564561353761491</v>
+        <v>-0.1234931005910482</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.01542657567044614</v>
+        <v>-0.01408116260562053</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.2453192325149303</v>
+        <v>0.2003581858545758</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1432676815371039</v>
+        <v>0.1066962343141427</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1897561558689915</v>
+        <v>0.1615524607553951</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.08421183956084377</v>
+        <v>-0.09927732918431786</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.09071466129227446</v>
+        <v>-0.09779993422305466</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1590633600570328</v>
+        <v>0.1466817962289397</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.05965958510250147</v>
+        <v>0.07146367184379443</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.236</t>
+          <t>X &gt; -0.2357</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3416</v>
+        <v>3424</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.05967915772221488</v>
+        <v>-0.05827294572760877</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.02108340732364411</v>
+        <v>0.06729503156300609</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.357897727787126</v>
+        <v>-0.3556400370436705</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.445381581343959</v>
+        <v>-0.45933263816476</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5591714945028841</v>
+        <v>-0.5398226550290914</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.304339589160044</v>
+        <v>-0.3254312967941004</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1979038122009484</v>
+        <v>-0.2109049042677427</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.08151625541946572</v>
+        <v>0.05318934264818864</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2556334371609879</v>
+        <v>-0.3049511497002797</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1245713295111273</v>
+        <v>-0.1360790005882677</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3421605624965025</v>
+        <v>-0.3694165284163233</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3499349015279805</v>
+        <v>-0.3696439516353678</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.02209610545639151</v>
+        <v>-0.03487487089992669</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3067150742000422</v>
+        <v>-0.295039368322449</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.2212</t>
+          <t>X &gt; -0.221</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3300</v>
+        <v>3304</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.03082528643272298</v>
+        <v>-0.02827163118238474</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1426226192935331</v>
+        <v>0.143999225550381</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.221900731583716</v>
+        <v>-0.2194724189386505</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6058921639179076</v>
+        <v>-0.6041162227602968</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.6740604594641866</v>
+        <v>-0.6393702063272286</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5582295463192679</v>
+        <v>-0.5481827504622956</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3403680447684891</v>
+        <v>-0.2759090576054319</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.03433078474083828</v>
+        <v>0.01491677765287847</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.381381662999452</v>
+        <v>-0.3247192697405765</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2758707369232596</v>
+        <v>-0.2102911919599251</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.5848480620700869</v>
+        <v>-0.5354970147986791</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5942032136722375</v>
+        <v>-0.5681293089107839</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3779904306220132</v>
+        <v>-0.3276940151356271</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.57649720463791</v>
+        <v>-0.5023779666795818</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.2065</t>
+          <t>X &gt; -0.2063</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>3165</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.05036047497879537</v>
+        <v>-0.09305021351257636</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1376958561997981</v>
+        <v>0.1563161452494271</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3517724982522168</v>
+        <v>-0.3638041495423749</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4425069506234465</v>
+        <v>-0.4234935680433338</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6335742814969194</v>
+        <v>-0.6283825194217911</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6202911609527391</v>
+        <v>-0.6399571901763252</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3577792979966858</v>
+        <v>-0.353061936589782</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.09883784077332081</v>
+        <v>-0.06060085811056837</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.3003155751140696</v>
+        <v>-0.2555513503437297</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3116651959945571</v>
+        <v>-0.2578949390576</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7515168823280121</v>
+        <v>-0.7147999995478855</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7803298832112375</v>
+        <v>-0.7514199920408018</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.631760357377722</v>
+        <v>-0.5778575394577175</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8167672032017421</v>
+        <v>-0.7395551734929029</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.1917</t>
+          <t>X &gt; -0.1915</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2804251923453336</v>
+        <v>0.2356954753431992</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4443870282755853</v>
+        <v>0.4282500574020816</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3119885642375095</v>
+        <v>-0.3272110483082074</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5433676284071964</v>
+        <v>-0.5590501244891257</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.752926083541027</v>
+        <v>-0.71946006780869</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5541713832945021</v>
+        <v>-0.5453263082794706</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3430237543949843</v>
+        <v>-0.3100271196358051</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2183764218503583</v>
+        <v>-0.1839493242809098</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3451047979655186</v>
+        <v>-0.2866897729441789</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3731958493907044</v>
+        <v>-0.2884203596782697</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8737549958165829</v>
+        <v>-0.7885160850834794</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8065037336650605</v>
+        <v>-0.6974654279553434</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6349386106471187</v>
+        <v>-0.5007127987809312</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7050609485862722</v>
+        <v>-0.5476232146346831</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.177</t>
+          <t>X &gt; -0.1768</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.6161245751091471</v>
+        <v>0.6052065916362537</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6911050340067675</v>
+        <v>0.7087764944322075</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1586874001120222</v>
+        <v>0.177344874447968</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.433730264283092</v>
+        <v>-0.4156626506024139</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.7311388813842967</v>
+        <v>-0.698371344050031</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.6402342254587836</v>
+        <v>-0.6321262727354053</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.208771150451021</v>
+        <v>-0.1764312432001063</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.05643167310906705</v>
+        <v>-0.0226426610705488</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1862369542016964</v>
+        <v>-0.1284620860421128</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1414551311234362</v>
+        <v>-0.05728206100510391</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.7246834745178319</v>
+        <v>-0.6400799956324263</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.7247168844474388</v>
+        <v>-0.6163366661849139</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4910480543472246</v>
+        <v>-0.3574498423184451</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5406049024001121</v>
+        <v>-0.3837922436421479</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.1622</t>
+          <t>X &gt; -0.1621</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2770</v>
+        <v>2766</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.8042825254223303</v>
+        <v>0.7798375605070902</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9981505839830405</v>
+        <v>0.9681716828711231</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4589748670980498</v>
+        <v>0.4659738247082643</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.04768376519903939</v>
+        <v>0.08971180663154144</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2378982066692146</v>
+        <v>-0.1464643046746801</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.05947582296587228</v>
+        <v>0.09016792419485853</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5884838752520452</v>
+        <v>0.6441177641089553</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4463249787577297</v>
+        <v>0.5036646132700824</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3853428222349535</v>
+        <v>0.4305387141838963</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4379511017173741</v>
+        <v>0.5105423821035515</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1638619699002248</v>
+        <v>-0.09128425487577374</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.05728165147991859</v>
+        <v>0.07534235233727316</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2084880728239966</v>
+        <v>0.3670969348117623</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.1815161418231028</v>
+        <v>0.3992220571308209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.1475</t>
+          <t>X &gt; -0.1473</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2623</v>
+        <v>2619</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6643374959620303</v>
+        <v>0.6781279612909401</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.9593656613808577</v>
+        <v>1.004076496600923</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5645942766258187</v>
+        <v>0.5721559958768978</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.06766628317888745</v>
+        <v>-0.06161021109475229</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1865886994083965</v>
+        <v>-0.1308517155441891</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0345367598873807</v>
+        <v>0.06556877845610387</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.4073178226570491</v>
+        <v>0.4631028381424471</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5883620267544103</v>
+        <v>0.6081902763081644</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.5655041554012925</v>
+        <v>0.647582691990003</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.8211896289913696</v>
+        <v>0.8928644586358843</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.006499908016728284</v>
+        <v>0.1159863249600406</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2314994862203221</v>
+        <v>0.3268831119622035</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6119586214696184</v>
+        <v>0.733557945994022</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.5708242755085848</v>
+        <v>0.7153252211441767</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; -0.1327</t>
+          <t>X &gt; -0.1326</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.9286388898413165</v>
+        <v>0.9430961849209467</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.9099395260547425</v>
+        <v>0.9537074119841407</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3926691621245268</v>
+        <v>0.4373703227294996</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.03289838901219611</v>
+        <v>0.07685796018448343</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7095561293754571</v>
+        <v>-0.6167230156673185</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2896831205652006</v>
+        <v>-0.2622047628884445</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5239323674532415</v>
+        <v>0.5761992214455631</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6285256264839774</v>
+        <v>0.7233619657618462</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6492094560779904</v>
+        <v>0.7272557236050261</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9834474584414679</v>
+        <v>1.088551785209333</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4112493626557594</v>
+        <v>0.5166140348534611</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.8131244525365986</v>
+        <v>0.942578075038135</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.127967474274236</v>
+        <v>1.283014754113864</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.272037138383986</v>
+        <v>1.450326882169286</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; -0.118</t>
+          <t>X &gt; -0.1179</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.060658980464325</v>
+        <v>0.990548677094516</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.429235315909075</v>
+        <v>1.47694446732396</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.9024797692534676</v>
+        <v>0.9070726172743377</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5047682652395409</v>
+        <v>0.4645216078505285</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2534948910237773</v>
+        <v>-0.2008613948363092</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.04387913861130954</v>
+        <v>0.07192412398261894</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.191020957083815</v>
+        <v>1.244205066901593</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.38387312279994</v>
+        <v>1.438874288024195</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.410880407544212</v>
+        <v>1.445935144321126</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.880803230220074</v>
+        <v>1.943110526518034</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.280149586258162</v>
+        <v>1.342668890078386</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.930453827482815</v>
+        <v>2.017304143515489</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.302207945572839</v>
+        <v>2.458782060192526</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.219980551364706</v>
+        <v>2.355559198738057</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.1032</t>
+          <t>X &gt; -0.1031</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2077</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.298573617997178</v>
+        <v>1.269377823644547</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.757681217759547</v>
+        <v>1.756494431314891</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.411056197953947</v>
+        <v>1.410902807949626</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.156110421946742</v>
+        <v>1.155615929568739</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1363572193565901</v>
+        <v>0.1849031391223619</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4337312489916769</v>
+        <v>0.45768865794129</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.745265473259451</v>
+        <v>1.793277152249772</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.855953208866069</v>
+        <v>1.905200771259786</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.698678322444401</v>
+        <v>1.771935432224097</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.29315047459793</v>
+        <v>2.392497799892503</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.655132031792711</v>
+        <v>1.755040067811386</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.315412928490844</v>
+        <v>2.439109549519088</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.665603914368575</v>
+        <v>2.814293462146402</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.31358318520175</v>
+        <v>2.485581944768413</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; -0.0885</t>
+          <t>X &gt; -0.0884</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1889</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.833536060519116</v>
+        <v>1.804340266166484</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.392810528598744</v>
+        <v>2.391623742154088</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.05097720631062</v>
+        <v>2.050823816306298</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.181202349898982</v>
+        <v>2.180707857520979</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.113532172134157</v>
+        <v>1.162078091899929</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.463844264236158</v>
+        <v>1.487801673185771</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.490833216775172</v>
+        <v>2.538844895765493</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.447269072723749</v>
+        <v>2.496516635117466</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.492163041134795</v>
+        <v>2.565420150914491</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.177448056345433</v>
+        <v>3.276795381640007</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.390428210949189</v>
+        <v>2.490336246967864</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.165939237841307</v>
+        <v>3.289635858869552</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.539859321531601</v>
+        <v>3.688548869309429</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.236214347088996</v>
+        <v>3.408213106655658</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; -0.07375</t>
+          <t>X &gt; -0.07367</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.896386405591613</v>
+        <v>2.84066106453038</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.067731506823684</v>
+        <v>3.100527974618281</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.732377828545168</v>
+        <v>2.766243018408218</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.684349852703953</v>
+        <v>2.71776796330898</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.373630115413363</v>
+        <v>1.455629404996785</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.205763503337224</v>
+        <v>2.263492212757441</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.36882498007818</v>
+        <v>3.451349797729364</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.495933401056739</v>
+        <v>3.580047358392392</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.494368951010493</v>
+        <v>3.602527781360237</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.367563642500002</v>
+        <v>4.443384099475097</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.568685419474512</v>
+        <v>3.644713330892635</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.434911462501255</v>
+        <v>4.535222517722445</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.54951996747662</v>
+        <v>4.675141880100362</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.359331672367439</v>
+        <v>4.508015517383271</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.059</t>
+          <t>X &gt; -0.05893</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1478</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.540734849032631</v>
+        <v>3.51153905468</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.621023722139299</v>
+        <v>3.619836935694643</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.09093434009062</v>
+        <v>3.090780950086298</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.815205491798068</v>
+        <v>2.814710999420065</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.803302948174633</v>
+        <v>1.851848867940404</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.57428996833746</v>
+        <v>2.598247377287073</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.113395576594968</v>
+        <v>4.161407255585289</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.593552913863711</v>
+        <v>4.642800476257428</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.870865750575035</v>
+        <v>4.944122860354732</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.509444924475218</v>
+        <v>5.608792249769792</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.966448772980925</v>
+        <v>5.066356808999601</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.01571190503855</v>
+        <v>6.139408526066795</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.136833040899702</v>
+        <v>6.28552258867753</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.821296701951674</v>
+        <v>5.993295461518336</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.04425</t>
+          <t>X &gt; -0.0442</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.137976477608973</v>
+        <v>3.154109854004616</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.481187778681949</v>
+        <v>3.526922988897674</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.493582517705413</v>
+        <v>3.540682963093154</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.216641537515272</v>
+        <v>3.26306904179765</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.248384557709485</v>
+        <v>3.34431704835999</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.034357935878774</v>
+        <v>4.106100122191144</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.171145947948112</v>
+        <v>5.267937920496244</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.762709225985475</v>
+        <v>5.861599862639387</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.946026743729803</v>
+        <v>6.0691260310087</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.887638892025336</v>
+        <v>7.038288485238539</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.11290516047525</v>
+        <v>6.263650890188188</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.450214908921772</v>
+        <v>7.62581110758569</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.007262752676766</v>
+        <v>8.208648291046309</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.581532604857692</v>
+        <v>7.805696413045375</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; -0.0295</t>
+          <t>X &gt; -0.02947</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.107906324755071</v>
+        <v>3.189888175113019</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.692329014126365</v>
+        <v>3.70671108995716</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.195761222185702</v>
+        <v>4.112973101642453</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.226185966572473</v>
+        <v>4.242857142857133</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.087098010283164</v>
+        <v>4.153608001905219</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.783673636724636</v>
+        <v>4.826393520724146</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.696967269474428</v>
+        <v>5.765737431498685</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.728900621695679</v>
+        <v>5.799904671115343</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.067120061979288</v>
+        <v>6.162932061978545</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.814007652874977</v>
+        <v>6.939103481163563</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.210104897808399</v>
+        <v>6.334963033627474</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.941089836590869</v>
+        <v>8.09312977099237</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.718543773696624</v>
+        <v>8.897971844428547</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.044079823124754</v>
+        <v>9.347016706443917</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.01475</t>
+          <t>X &gt; -0.01473</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>716</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.709028103543865</v>
+        <v>1.679832309191234</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.589462122211877</v>
+        <v>3.588275335767221</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.032679564272478</v>
+        <v>4.032526174268156</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.883575098922286</v>
+        <v>3.883080606544283</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.043609568172968</v>
+        <v>4.09215548793874</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.340983597808055</v>
+        <v>4.364941006757668</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.094262065357526</v>
+        <v>5.142273744347847</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.744511857324973</v>
+        <v>5.79375941971869</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.661183332087127</v>
+        <v>6.734440441866823</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.906236602796369</v>
+        <v>8.005583928090942</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.863546617720523</v>
+        <v>6.963454653739198</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.992896837114962</v>
+        <v>9.116593458143207</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.131405201678646</v>
+        <v>9.280094749456474</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.636470460843718</v>
+        <v>9.80846922041038</v>
       </c>
     </row>
     <row r="35">
@@ -3848,1509 +3848,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.4277</t>
+          <t>X &lt; -0.4273</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.555228547778903</v>
+        <v>6.526032753426271</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.558500286040378</v>
+        <v>8.557313499595722</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.958909624176897</v>
+        <v>6.958756234172576</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.31805043041586</v>
+        <v>14.31755593803786</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>18.5990379857539</v>
+        <v>18.64758390551967</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>15.28195418406369</v>
+        <v>15.30591159301331</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.99242454768908</v>
+        <v>14.0404362266794</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>13.52535590390234</v>
+        <v>13.57460346629606</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.64509663894583</v>
+        <v>8.718353748725526</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.02409350526658</v>
+        <v>15.12344083056115</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>16.02421162411483</v>
+        <v>16.1241196601335</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.85377049936171</v>
+        <v>14.97746712038995</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>13.22880036893987</v>
+        <v>13.3774899167177</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>13.4545360191664</v>
+        <v>13.62653477873307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.413</t>
+          <t>X &lt; -0.4125</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11.23589812875768</v>
+        <v>11.52497589441126</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>6.084889026844301</v>
+        <v>5.555833896974704</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.57507339430164</v>
+        <v>6.916481873572287</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13.78494455558911</v>
+        <v>14.06390977443608</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.24665500249342</v>
+        <v>13.57466063348416</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.234294518854178</v>
+        <v>8.58428825756625</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.034539911800401</v>
+        <v>8.523632168340789</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.02764825916411</v>
+        <v>4.549027478132885</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.19675459821655</v>
+        <v>2.757668904083815</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.771614562948635</v>
+        <v>7.196998218005668</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.681957652476051</v>
+        <v>5.238471805557303</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.831380052618982</v>
+        <v>5.296638542922196</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.641317694880804</v>
+        <v>3.147094651446082</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.867053345107337</v>
+        <v>2.518946531005319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.3982</t>
+          <t>X &lt; -0.3978</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.873922679143064</v>
+        <v>7.362499640081168</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.682091424788915</v>
+        <v>3.231551854288369</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.80344907229194</v>
+        <v>7.296412592088316</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.80464195781578</v>
+        <v>10.61101000909918</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>9.621191114397512</v>
+        <v>9.484818192988023</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.757274821451951</v>
+        <v>4.662062310533059</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.238348896466839</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.600955794504173</v>
+        <v>-1.596910615508861</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.66193795102695</v>
+        <v>-0.9969405494864247</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7139497042560876</v>
+        <v>0.7270015703355384</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1359127443266885</v>
+        <v>0.5228611227994477</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.7466958822939418</v>
+        <v>-0.05591481499489248</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.747491896897671</v>
+        <v>-2.998843442195664</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.812078827316306</v>
+        <v>-4.02368393049877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.3835</t>
+          <t>X &lt; -0.3831</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.029722267337988</v>
+        <v>5.690946376171212</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.354706387040125</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.02376478951912</v>
+        <v>4.243131831801193</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.345479294809607</v>
+        <v>7.547619047619044</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.743359954479878</v>
+        <v>6.000168848466068</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.317329728795812</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.232619369529644</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.021683316810282</v>
+        <v>-2.719142947932269</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.018835686099024</v>
+        <v>-1.697914498868009</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2091800143437794</v>
+        <v>0.1237595658196469</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.4138811726039719</v>
+        <v>-0.08038088171644375</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.44333280748269</v>
+        <v>-1.080415202552608</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.991143235264182</v>
+        <v>-3.591975245518555</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.361152265888713</v>
+        <v>-4.930231970804769</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.3687</t>
+          <t>X &lt; -0.3683</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.43763600566475</v>
+        <v>5.597996283221121</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.016495161469692</v>
+        <v>2.213017396263474</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.431678527845882</v>
+        <v>3.621081209750564</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.37185842256546</v>
+        <v>5.552767052767045</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.928591493904158</v>
+        <v>4.162617010914225</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.963522084625211</v>
+        <v>2.183150277480905</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.878811725359043</v>
+        <v>2.122494188255445</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.75567773290733</v>
+        <v>-1.496491725281054</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9116825138644984</v>
+        <v>-0.6325634335169497</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.04835344093686444</v>
+        <v>0.3454097874698761</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7486296582422796</v>
+        <v>1.042170240834686</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1219695649680048</v>
+        <v>-0.2510143731517829</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.709541232761048</v>
+        <v>-3.799325452868764</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.936294270317319</v>
+        <v>-4.000731041303844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.354</t>
+          <t>X &lt; -0.3536</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>258</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.108231256287354</v>
+        <v>4.079035461934723</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5590606670994873</v>
+        <v>0.5578738806548316</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.48987067769329</v>
+        <v>2.489717287688968</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.620095821281652</v>
+        <v>2.619601328903649</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.081806268185957</v>
+        <v>2.130352187951729</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.05359890247220278</v>
+        <v>0.07755631142181585</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.356485442430845</v>
+        <v>0.4044971214211657</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.211358395154342</v>
+        <v>-3.162110832760625</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.272340551677118</v>
+        <v>-3.199083441897422</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.347065549557357</v>
+        <v>-3.247718224262783</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.388976010143146</v>
+        <v>-2.289067974124471</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.904985454687036</v>
+        <v>-3.781288833658792</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.3392</t>
+          <t>X &lt; -0.3389</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.833077143527085</v>
+        <v>3.952473209126616</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5084843761579094</v>
+        <v>-0.3517923114033792</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.485822737380566</v>
+        <v>1.635422081234289</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.957344809296579</v>
+        <v>2.105442176870739</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.419055256200885</v>
+        <v>1.616193035918819</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.355243069112831</v>
+        <v>-1.172245935058164</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.439953428378999</v>
+        <v>-1.232902024283625</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.954803642131623</v>
+        <v>-3.739551111197578</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.015785798654399</v>
+        <v>-3.776523720334374</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.207001523311895</v>
+        <v>-4.940488355571127</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.705218039933861</v>
+        <v>-3.44394853099837</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.377324529216764</v>
+        <v>-5.086462065742325</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.845256952496044</v>
+        <v>-7.522436318836768</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-7.619521302269511</v>
+        <v>-7.2733914568214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.3245</t>
+          <t>X &lt; -0.3241</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.627443102592586</v>
+        <v>2.25911894434379</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.08746443986931496</v>
+        <v>0.0605572438033164</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.550278194433162</v>
+        <v>1.512973101642466</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.370905814801702</v>
+        <v>1.335164835164832</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.451811308145636</v>
+        <v>1.461300309597526</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.037192371197605</v>
+        <v>-1.03514494081432</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.431500253683581</v>
+        <v>-1.403493337732087</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.756154036789205</v>
+        <v>-3.715479944269269</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4.126733716531795</v>
+        <v>-4.060144861098379</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.595847559301284</v>
+        <v>-5.499358057297975</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.94296357824259</v>
+        <v>-3.857344658680212</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.456573041986346</v>
+        <v>-5.337639459776867</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.805516464959197</v>
+        <v>-6.655874309417612</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.270183291512843</v>
+        <v>-6.099137139709946</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.3097</t>
+          <t>X &lt; -0.3094</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>371</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.775148659492601</v>
+        <v>2.745952865139969</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.183746328449935</v>
+        <v>-0.1849331148945907</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.038732960649476</v>
+        <v>1.038579570645155</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.977583441165066</v>
+        <v>1.977088948787063</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.169752109093629</v>
+        <v>1.218298028859401</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.036916987955927</v>
+        <v>-2.012959579006314</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.391169126197831</v>
+        <v>-2.34315744720751</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.745030222814762</v>
+        <v>-4.695782660421045</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.075554158313281</v>
+        <v>-5.002297048533585</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-5.925472954643141</v>
+        <v>-5.826125629348567</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.782465218024626</v>
+        <v>-4.682557182005951</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.556712402596531</v>
+        <v>-5.433015781568287</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.246405034885676</v>
+        <v>-6.097715487107848</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.751127605683408</v>
+        <v>-5.579128846116745</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.295</t>
+          <t>X &lt; -0.2947</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>415</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.254023728501799</v>
+        <v>1.224827934149168</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3657292017030258</v>
+        <v>0.3645424152583701</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.175777094056414</v>
+        <v>1.175623704052093</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.065038382223094</v>
+        <v>1.064543889845091</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.008676539970779</v>
+        <v>1.05722245973655</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.826479550876073</v>
+        <v>-1.80252214192646</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.911189910142241</v>
+        <v>-1.86317823115192</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.305969397302462</v>
+        <v>-4.256721834908745</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.125987698403556</v>
+        <v>-4.052730588623859</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.457834205576795</v>
+        <v>-5.358486880282221</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.734824520463491</v>
+        <v>-3.634916484444815</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.94141022352985</v>
+        <v>-3.817713602501605</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.602524932264956</v>
+        <v>-4.453835384487128</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.376789282038423</v>
+        <v>-4.204790522471761</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.2802</t>
+          <t>X &lt; -0.2799</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.49757859312156</v>
+        <v>1.451344277896737</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1136074999422689</v>
+        <v>-0.1318328072591157</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7819436959478594</v>
+        <v>0.7592257783019818</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4820613126544941</v>
+        <v>0.4608442948914018</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1588255229996633</v>
+        <v>0.1857279162521195</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.909391845214714</v>
+        <v>-1.99849918313852</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.854317258244322</v>
+        <v>-2.917524371076418</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.041816009557941</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.027529348876413</v>
+        <v>-4.064106564630897</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.307555672087993</v>
+        <v>-5.317119694802102</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.361719195939585</v>
+        <v>-3.375337395557075</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.757448570465982</v>
+        <v>-3.746355207548405</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.392653187220255</v>
+        <v>-4.356105408790341</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.521756246671139</v>
+        <v>-3.463283722740641</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.2655</t>
+          <t>X &lt; -0.2652</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6381765970648914</v>
+        <v>0.7487336127294029</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.02782991187795147</v>
+        <v>0.09665522403538063</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.089686037960576</v>
+        <v>1.378894889351955</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4637675142521545</v>
+        <v>0.950119712689542</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.8706575452774459</v>
+        <v>0.9371900914574596</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7223275933294317</v>
+        <v>-0.3679990026403459</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.56318161989239</v>
+        <v>-1.26347605164738</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.542537598272695</v>
+        <v>-3.317731351398734</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.225447921147087</v>
+        <v>-3.069398765089126</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.264402634301149</v>
+        <v>-4.171819306030415</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.767780541143566</v>
+        <v>-2.580131305995167</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.355330555139844</v>
+        <v>-2.333285323347255</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.531625075750043</v>
+        <v>-3.483160231043158</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.30588942552351</v>
+        <v>-3.234115369027791</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.2507</t>
+          <t>X &lt; -0.2505</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9959051615186283</v>
+        <v>0.9100836148524323</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.04697072408394121</v>
+        <v>-0.02162767225782147</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.63895430621632</v>
+        <v>1.701898183075684</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.603616535897388</v>
+        <v>1.760312281519461</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.727578638430842</v>
+        <v>1.689555714323518</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3693235289930783</v>
+        <v>0.5818763357814376</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.04651265808765714</v>
+        <v>0.1198357921544186</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.672521699225392</v>
+        <v>-1.405514048096478</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7401263723044664</v>
+        <v>-0.5318047801267198</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.424482254727032</v>
+        <v>-1.265674113564607</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.02644572608561901</v>
+        <v>0.1055900963337422</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.1047390354663378</v>
+        <v>-0.07381237776797178</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.352704458316168</v>
+        <v>-1.29541658532353</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9614058941823558</v>
+        <v>-1.046371723308162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.236</t>
+          <t>X &lt; -0.2357</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5687293595365688</v>
+        <v>0.5539550274807041</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.169261512765452</v>
+        <v>-0.05429169555816316</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.62108103710132</v>
+        <v>1.579918708337019</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.035397089780602</v>
+        <v>2.067438148443735</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.775516627593987</v>
+        <v>2.636125484422699</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.368345202683628</v>
+        <v>1.448802484309581</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.999543934326546</v>
+        <v>1.045961835425757</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.4652638682104921</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.323765861289758</v>
+        <v>1.54366342625422</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3318016104144519</v>
+        <v>0.3771316501776525</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.263464088517892</v>
+        <v>1.380802243782625</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.155796786327755</v>
+        <v>1.237762539353945</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.2586722488038262</v>
+        <v>-0.2078273069151635</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.961381583240879</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.2212</t>
+          <t>X &lt; -0.221</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3606801000581541</v>
+        <v>0.3470310322558774</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3390754892156167</v>
+        <v>-0.3388193033682185</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7858537643740533</v>
+        <v>0.7635697603536755</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.318108916788539</v>
+        <v>2.273681515617</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.750693150100616</v>
+        <v>2.569875944488949</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.146057010923982</v>
+        <v>2.073100107550495</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.400450813335624</v>
+        <v>1.121133114951924</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.0398538401834756</v>
+        <v>-0.2381505509734936</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.602327020325376</v>
+        <v>1.353316677363161</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8740627252120561</v>
+        <v>0.5974668987327547</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.007561080333858</v>
+        <v>1.786770262543136</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.920284731472634</v>
+        <v>1.794215416348223</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.205555134653146</v>
+        <v>0.9858945497425537</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.867700873706511</v>
+        <v>1.546291192538227</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.2065</t>
+          <t>X &lt; -0.2063</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.3688249021081305</v>
+        <v>0.5031670310885019</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.253927849739263</v>
+        <v>-0.3100578261982534</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.091274022829765</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.36060735249086</v>
+        <v>1.278103044496483</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.128995484844964</v>
+        <v>2.076684924982139</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.964936111774541</v>
+        <v>1.997235409841188</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.209279454281045</v>
+        <v>1.17252057641133</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1742479229178713</v>
+        <v>0.04393759292604926</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.052722968900319</v>
+        <v>0.8876488487962675</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8291089742405973</v>
+        <v>0.6370416254934597</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.190169820155774</v>
+        <v>2.039297398952549</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.181136389253567</v>
+        <v>2.05428679578575</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.822085643931047</v>
+        <v>1.615862227055224</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.318473444259446</v>
+        <v>2.028590205408712</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.1917</t>
+          <t>X &lt; -0.1915</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6019059480412281</v>
+        <v>-0.4702206190846283</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.064579187818367</v>
+        <v>-1.007989454507445</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.7931999535384264</v>
+        <v>0.8263246002800528</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.433792811705729</v>
+        <v>1.461038961038959</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.142780573399797</v>
+        <v>2.02348971255126</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.479784178072876</v>
+        <v>1.43732248247278</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.9859285174853269</v>
+        <v>0.8807784524649591</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.477963381784356</v>
+        <v>0.3743572258598675</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.022361932808266</v>
+        <v>0.8446672217958948</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.871364288955867</v>
+        <v>0.6204563148015865</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.199439826470957</v>
+        <v>1.931943820452723</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.917581298112275</v>
+        <v>1.585437463300053</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.551321221581205</v>
+        <v>1.151500717022493</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.645518874521031</v>
+        <v>1.178209366994366</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.177</t>
+          <t>X &lt; -0.1768</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.299171939254805</v>
+        <v>-1.259102946759462</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.481987931102253</v>
+        <v>-1.508474693564644</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4460571818226029</v>
+        <v>-0.4854100834828472</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9538091515750153</v>
+        <v>0.9017568192325456</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.769003210512302</v>
+        <v>1.671826625387006</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.458082592952934</v>
+        <v>1.423152029638246</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5183809531635717</v>
+        <v>0.4346749821880636</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.01459153495113696</v>
+        <v>-0.06762779641712058</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.491069537924858</v>
+        <v>0.3462789344399582</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1794934300890247</v>
+        <v>-0.02593716924294398</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.500050889145363</v>
+        <v>1.280040332244241</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.417459465753588</v>
+        <v>1.140686774249701</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.9624510209305512</v>
+        <v>0.6291861883568259</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9885270078327579</v>
+        <v>0.5985664617456976</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.1622</t>
+          <t>X &lt; -0.1621</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1350</v>
+        <v>1365</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.490453814833693</v>
+        <v>-1.421577717484958</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.889458951792022</v>
+        <v>-1.805707210696426</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9967926854288933</v>
+        <v>-0.9986548053342901</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1654718941766262</v>
+        <v>-0.2480519480519519</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.5134506031107549</v>
+        <v>0.3210024706097343</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1793017380045541</v>
+        <v>-0.2400303685693714</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.181905787653754</v>
+        <v>-1.281492889201019</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.019549380953883</v>
+        <v>-1.124894745368977</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.7453803983546621</v>
+        <v>-0.8304985949557633</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.038087271014319</v>
+        <v>-1.176382274862732</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1282552932481238</v>
+        <v>-0.0246860891795464</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1654780926394253</v>
+        <v>-0.4375212897245291</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6181492355476621</v>
+        <v>-0.9383385508862503</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6472042753449756</v>
+        <v>-1.088148128720924</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.1475</t>
+          <t>X &lt; -0.1473</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1497</v>
+        <v>1512</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.023962388150245</v>
+        <v>-1.034701988821404</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.540743608024947</v>
+        <v>-1.599850589832862</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.038597646284259</v>
+        <v>-1.039883103216368</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.05609217936254396</v>
+        <v>0.04495963957198512</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.3507460130823361</v>
+        <v>0.2489400203141585</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1125140543384191</v>
+        <v>-0.1657117424337429</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6929125453639742</v>
+        <v>-0.7830446619838654</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.124060123480639</v>
+        <v>-1.14752615892418</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.9493396949383026</v>
+        <v>-1.083013883967396</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.563241845463452</v>
+        <v>-1.673297574245403</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1982783357245381</v>
+        <v>-0.3894594086167515</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6601865965335421</v>
+        <v>-0.8228543769600805</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.243508090532202</v>
+        <v>-1.445848380290556</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.247961345039919</v>
+        <v>-1.491078531651326</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; -0.1327</t>
+          <t>X &lt; -0.1326</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1671</v>
+        <v>1684</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.2338851516745</v>
+        <v>-1.243170163130948</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.210343359486473</v>
+        <v>-1.263100230797555</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6224264215517934</v>
+        <v>-0.6817171638442687</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1032277817785356</v>
+        <v>-0.1658795749704893</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.057443034520404</v>
+        <v>0.9126156805821282</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.3756344441152137</v>
+        <v>0.3318308729700163</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7490203738325221</v>
+        <v>-0.819951509956077</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.005037584182368</v>
+        <v>-1.135598287464532</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9143823270374227</v>
+        <v>-1.02220707360464</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.552781157563842</v>
+        <v>-1.695493675234538</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7691266033469972</v>
+        <v>-0.9190381519089783</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.418851368864324</v>
+        <v>-1.599159671475014</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.806220095693782</v>
+        <v>-2.021315989399355</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.086262723380088</v>
+        <v>-2.333743388567967</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; -0.118</t>
+          <t>X &lt; -0.1179</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1847</v>
+        <v>1860</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.190593449889185</v>
+        <v>-1.095269326221739</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.644549676045735</v>
+        <v>-1.689442756196684</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.149952087470552</v>
+        <v>-1.146567251110078</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6679030766657732</v>
+        <v>-0.6138273491214647</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.331355185587725</v>
+        <v>0.2632923250726904</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.09621617933058957</v>
+        <v>-0.1303516612886995</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.446028292799085</v>
+        <v>-1.500893527258675</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.776434094732238</v>
+        <v>-1.831070677223344</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.700605825338947</v>
+        <v>-1.732242200756041</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.41356637249406</v>
+        <v>-2.473772055317127</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.724404461850661</v>
+        <v>-1.790372446780474</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.579944892220844</v>
+        <v>-2.669705889587661</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.971064023695604</v>
+        <v>-3.143618698290432</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.932832621612192</v>
+        <v>-3.080940282803404</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.1032</t>
+          <t>X &lt; -0.1031</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2043</v>
+        <v>2054</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.216324590845637</v>
+        <v>-1.179681249173392</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.683342999510593</v>
+        <v>-1.6731533824533</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.468373021498309</v>
+        <v>-1.460392515790957</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.214904575188626</v>
+        <v>-1.207918050941316</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1191094578215655</v>
+        <v>-0.1687380960104363</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4776223962703199</v>
+        <v>-0.4998916393146473</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.755444979198948</v>
+        <v>-1.795834620903058</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.952661583323277</v>
+        <v>-1.993299212379803</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.694700047801149</v>
+        <v>-1.761642974446907</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.420771445498858</v>
+        <v>-2.510945109701346</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.817242167591594</v>
+        <v>-1.911269343620944</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.538635309693582</v>
+        <v>-2.653562836011524</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.834670736617383</v>
+        <v>-2.97404762029165</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.533645782931863</v>
+        <v>-2.698942397743046</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; -0.0885</t>
+          <t>X &lt; -0.0884</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2231</v>
+        <v>2242</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.455960593814211</v>
+        <v>-1.423637323778337</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.929819466442595</v>
+        <v>-1.919375866564579</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.766088494972308</v>
+        <v>-1.757333156679778</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.88007540626419</v>
+        <v>-1.87046434914997</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9217236321462607</v>
+        <v>-0.959230736433291</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.270185594344262</v>
+        <v>-1.284717590386968</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.090674604953655</v>
+        <v>-2.122034911764985</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.131908827800494</v>
+        <v>-2.164152268386431</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.079734707908479</v>
+        <v>-2.133062597567509</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.771653240104165</v>
+        <v>-2.844244693368935</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.14677132289254</v>
+        <v>-2.222943425169852</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.849465193072156</v>
+        <v>-2.94287735913241</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.111291180051794</v>
+        <v>-3.225166809160406</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.906380529142474</v>
+        <v>-3.041564917106491</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; -0.07375</t>
+          <t>X &lt; -0.07367</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2437</v>
+        <v>2449</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.909487459105783</v>
+        <v>-1.860233677039702</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.030035974149435</v>
+        <v>-2.041277532554012</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.91334409658851</v>
+        <v>-1.926051288601442</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.884233162476342</v>
+        <v>-1.896793121477963</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9292797003625921</v>
+        <v>-0.9814611600150442</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.550529123399293</v>
+        <v>-1.582153487822858</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.309115491354149</v>
+        <v>-2.354132275341705</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.468213132784726</v>
+        <v>-2.513537284078133</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.384772222248323</v>
+        <v>-2.447581385454221</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.090149620452188</v>
+        <v>-3.127631129517226</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.576420412227264</v>
+        <v>-2.616912985948382</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.217036714734519</v>
+        <v>-3.271292913626155</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.24628784280786</v>
+        <v>-3.318354686183696</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.162774420787919</v>
+        <v>-3.25175830376434</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.059</t>
+          <t>X &lt; -0.05893</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2642</v>
+        <v>2653</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.89711188740818</v>
+        <v>-1.872452410033276</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.944400541081222</v>
+        <v>-1.935690410980918</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.754118137075423</v>
+        <v>-1.746786658117301</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.604008847419458</v>
+        <v>-1.59709779518267</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9907508186527068</v>
+        <v>-1.014686513496734</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.46548841652735</v>
+        <v>-1.473268260561085</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.285143254664156</v>
+        <v>-2.303435500832144</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.619131410915827</v>
+        <v>-2.636763249155436</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.698046997177798</v>
+        <v>-2.72924250536532</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.150190934078104</v>
+        <v>-3.194618761967781</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.88120209123808</v>
+        <v>-2.927085159143616</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.507420102683376</v>
+        <v>-3.564497347651695</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.529264808911151</v>
+        <v>-3.600747070416979</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.396972969095508</v>
+        <v>-3.482534744743425</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.04425</t>
+          <t>X &lt; -0.0442</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2892</v>
+        <v>2904</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.258885049467231</v>
+        <v>-1.25882625752326</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.406151710375042</v>
+        <v>-1.418391790701271</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.507197311315672</v>
+        <v>-1.519616949815521</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.393174898190082</v>
+        <v>-1.405873124816161</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.361673526271446</v>
+        <v>-1.39634050478891</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.735494922708227</v>
+        <v>-1.757672413341787</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.181411881158411</v>
+        <v>-2.212414406357723</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.492338060360495</v>
+        <v>-2.522775741255785</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.50062535846736</v>
+        <v>-2.541674331971265</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.987039424241502</v>
+        <v>-3.03792540466862</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.689815468712446</v>
+        <v>-2.742264348553469</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.293455585350323</v>
+        <v>-3.353945246213421</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.487910928375207</v>
+        <v>-3.558826778635137</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.347527004713349</v>
+        <v>-3.42929183350099</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; -0.0295</t>
+          <t>X &lt; -0.02947</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3118</v>
+        <v>3131</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9318901602053842</v>
+        <v>-0.9515876518590005</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.120856117208412</v>
+        <v>-1.118424131169149</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.370862003079971</v>
+        <v>-1.33616757308701</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.383502584713703</v>
+        <v>-1.380383863191895</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.297240444243663</v>
+        <v>-1.311360150961015</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.55853637702905</v>
+        <v>-1.563093577077701</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.818274247491637</v>
+        <v>-1.829928597819354</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.884298076937782</v>
+        <v>-1.896397528438378</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.928224503452761</v>
+        <v>-1.948292427817371</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.248584651305897</v>
+        <v>-2.276685992520648</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.083592871663868</v>
+        <v>-2.112707674732448</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.672874542343571</v>
+        <v>-2.707572431369584</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.883484615821232</v>
+        <v>-2.92603837268512</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.025366915213837</v>
+        <v>-3.107023536290043</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.01475</t>
+          <t>X &lt; -0.01473</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3404</v>
+        <v>3415</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3006409354216828</v>
+        <v>-0.2930756521915328</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6963175802726482</v>
+        <v>-0.6938141507781737</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8704752653078245</v>
+        <v>-0.8676456957889442</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.8417098761884105</v>
+        <v>-0.8388946819603831</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.8369244399818569</v>
+        <v>-0.8452237737957162</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.9340234427389547</v>
+        <v>-0.9364460936492023</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.061635138725876</v>
+        <v>-1.069095999243565</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.249049636146403</v>
+        <v>-1.256190038034035</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.382222965078945</v>
+        <v>-1.394377879541914</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.717520839436169</v>
+        <v>-1.734514535800457</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.524704321440218</v>
+        <v>-1.542450658590198</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.002733614569053</v>
+        <v>-2.024341695206054</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.995798466932257</v>
+        <v>-2.02310543894383</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.135910372746721</v>
+        <v>-2.168063820642473</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3706</v>
+        <v>3717</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1012440757077826</v>
+        <v>-0.09724319217920652</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2728444581866682</v>
+        <v>-0.2718890709438853</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4110058731635533</v>
+        <v>-0.4097736794734175</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.5353351247218043</v>
+        <v>-0.5336923607650803</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4669433014406366</v>
+        <v>-0.4717274785027286</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.5857168230666048</v>
+        <v>-0.5870292980678045</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4404212983938649</v>
+        <v>-0.4452185298332125</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.7581790981749279</v>
+        <v>-0.7621957855056607</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.5889291976259869</v>
+        <v>-0.5964983517774911</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.9659042214895024</v>
+        <v>-0.9756774916931974</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.7782909177322637</v>
+        <v>-0.7886928803510216</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.106510755105994</v>
+        <v>-1.118970255896578</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.134127468658164</v>
+        <v>-1.149688187846877</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.298160682372618</v>
+        <v>-1.316206322880824</v>
       </c>
     </row>
   </sheetData>
